--- a/Streamlit/Data/consolidated_dataset.xlsx
+++ b/Streamlit/Data/consolidated_dataset.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E410"/>
+  <dimension ref="A1:E404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4836,7 +4836,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Column List</t>
+          <t>Behavioural Economics</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -4859,7 +4859,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Concept</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -4882,7 +4882,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -4905,7 +4905,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4915,13 +4915,13 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
-It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
+          <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
+Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -4933,7 +4933,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -4956,357 +4956,376 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Dot Py Categorization Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>General Definition</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Dot Py Categorization Reference List</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Guidance</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Dot Py Categorization Reference List</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Information</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Dot Py Categorization Reference List</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Dot Py Categorization Reference List</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Dot Py Categorization Reference List</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Regularization</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Dot Py Categorization Reference List</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Dot Py Categorization Reference List</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Dot Py Categorization Reference List</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Transformation</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Dot Py Parameter Reference List</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Behavioural Economics</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Dot Py Parameter Reference List</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Best Linear Unbiased Estimator</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Dot Py Parameter Reference List</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Categorization Values Currently in Use</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Dot Py Parameter Reference List</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Data Collection</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
-Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Dot Py Parameter Reference List</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Data Dictionary</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Dot Py Parameter Reference List</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Data Preparation</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
         <is>
           <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
 Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
 Where operational changes are necessary, or a prerequisite, need to understand how these will documented and escalated or addressed.</t>
         </is>
       </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Function cleans, reshapes, filters, joins, or transforms data into usable form.</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Default Python String Taxonomy</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Dot Py Categorization Reference List</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Dot Py Parameter Reference List</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Dot Py String Classification</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Function creates derived variables, metrics, flags, or analytical features</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Goal Setting</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Documentation Taxonomy Categorization</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Reference List</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Problem Solving Framework</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -5316,7 +5335,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Documentation Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5326,14 +5345,10 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Function cleans, reshapes, filters, joins, or transforms data into usable form.</t>
-        </is>
-      </c>
+          <t>Statistics</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -5343,7 +5358,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5353,7 +5368,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -5366,7 +5381,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5376,14 +5391,10 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
-        </is>
-      </c>
+          <t>Excel File Creation</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -5393,7 +5404,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5403,14 +5414,10 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Function creates derived variables, metrics, flags, or analytical features</t>
-        </is>
-      </c>
+          <t>File Manipulation/ Management</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -5420,12 +5427,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5433,7 +5440,11 @@
           <t>General Definition</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Categorization</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -5443,24 +5454,20 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Comprehensive List of all Values utilized in Organizational Taxonomy in the Column Process</t>
-        </is>
-      </c>
+          <t>Manual File Creator</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -5470,7 +5477,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5480,14 +5487,10 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
-        </is>
-      </c>
+          <t>Python String Documentation</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -5497,7 +5500,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Dot Py String Taxonomy Categorization</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5507,7 +5510,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -5520,22 +5523,22 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>How does Time Impact?</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
+          <t>What time-based changes or aggregates could capture trends or stability? Differences, growth rates, or rolling averages often reflect momentum or consistency, which are strong predictors of future behavior.</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -5547,20 +5550,24 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>Include Interactions</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>What combinations or interactions might reflect how factors work together? Some outcomes are driven by the interaction between variables (e.g., high balance and high transaction frequency), so combining features can expose relationships a model might miss.</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -5570,22 +5577,22 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Ratios or Observed Values</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+          <t>What ratios or proportions could better represent behavior than raw values? Many real-world patterns depend on relative size (e.g., debt-to-income, usage-to-capacity), so ratios often reveal signal that absolute values hide.</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -5597,20 +5604,24 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>Achievable</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -5620,20 +5631,24 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Process Values Currently in Use</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>Measurable</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -5643,20 +5658,24 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Dot Py Parameter Reference List</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Statistics</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
+          <t>Relevant</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -5666,22 +5685,22 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>How does Time Impact?</t>
+          <t>Specific</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>What time-based changes or aggregates could capture trends or stability? Differences, growth rates, or rolling averages often reflect momentum or consistency, which are strong predictors of future behavior.</t>
+          <t>Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -5693,22 +5712,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Include Interactions</t>
+          <t>Time Bound</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>What combinations or interactions might reflect how factors work together? Some outcomes are driven by the interaction between variables (e.g., high balance and high transaction frequency), so combining features can expose relationships a model might miss.</t>
+          <t>Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -5720,22 +5739,22 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Ratios or Observed Values</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>What ratios or proportions could better represent behavior than raw values? Many real-world patterns depend on relative size (e.g., debt-to-income, usage-to-capacity), so ratios often reveal signal that absolute values hide.</t>
+          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -5747,22 +5766,22 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Achievable</t>
-        </is>
-      </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
+          <t>Specific: Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -5774,22 +5793,22 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Measurable</t>
-        </is>
-      </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
+          <t>Measurable: Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -5801,22 +5820,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Relevant</t>
-        </is>
-      </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
+          <t>Achievable: Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -5828,22 +5847,22 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Specific</t>
-        </is>
-      </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
+          <t>Relevant: Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -5855,22 +5874,22 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Time Bound</t>
-        </is>
-      </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
+          <t>Time Bound: Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -5892,12 +5911,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -5914,17 +5933,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Specific: Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
+          <t>Desired State Metrics: Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -5941,17 +5960,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Measurable: Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
+          <t>Current State Analysis: Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -5968,17 +5987,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Achievable: Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
+          <t>Root Cause Assessment: Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -5995,17 +6014,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Relevant: Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
+          <t>Historical Overview: Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -6022,17 +6041,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Time Bound: Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
+          <t>Baseline Metrics (Current State): Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -6049,7 +6068,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6059,7 +6078,8 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+          <t>Understand KPIs which are meaningful.: Attempt to explicitly define outcomes and relevant KPIs for those outcomes. Where that can not happen, it is important to understand why that can not happen. What is happening if we don't have and follow metrics. IE. The Account Opening Process is not efficient and needs to improve, The Internet Banking Experience is poor, and does not attract customers. How do you monitor this, how can you define this, how can you prove this,  how do you expect this to change and measure that change.
+How will the project and efforts be measured where success can not be objectively measured? How will resources be allocated when it remains unclear what benefit or risk exists.</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -6076,7 +6096,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6086,7 +6106,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Desired State Metrics: Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+          <t>What Lens is Problem Defined?: Must be careful at how problem is defined. Is it defined in the context of the already identified solution, has it been validated and is the problem distinct from the analysis and potential solution, or have we leaked into the process.</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -6103,7 +6123,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6113,7 +6133,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Current State Analysis: Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+          <t>Stakeholder Investment?: How Invested are stakeholders in defining the problem? What is their view of the process/ project, how invested, interested and engaged are they. What are their personal goals and motivation, speed, accuracy, validation of ideology?</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -6130,7 +6150,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6140,7 +6160,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Root Cause Assessment: Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+          <t>Really Understand Problem Statement: Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk and the likelihood of not meeting expectations, frustration, or material change to purpose, scope or priority is inevitable.</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -6162,12 +6182,13 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Historical Overview: Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+          <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
+Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -6184,17 +6205,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Baseline Metrics (Current State): Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+          <t xml:space="preserve">Challenges from Missing Data: What concessions have we made due to a lack of data availability, and how are those going to undermine the work we plan on doing. </t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -6216,13 +6237,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Understand KPIs which are meaningful.: Attempt to explicitly define outcomes and relevant KPIs for those outcomes. Where that can not happen, it is important to understand why that can not happen. What is happening if we don't have and follow metrics. IE. The Account Opening Process is not efficient and needs to improve, The Internet Banking Experience is poor, and does not attract customers. How do you monitor this, how can you define this, how can you prove this,  how do you expect this to change and measure that change.
-How will the project and efforts be measured where success can not be objectively measured? How will resources be allocated when it remains unclear what benefit or risk exists.</t>
+          <t>Who is the Steward: Who is the Data Steward, are they involved, and operationally do we have integrity, consistency and availability to include?</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -6244,12 +6264,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>What Lens is Problem Defined?: Must be careful at how problem is defined. Is it defined in the context of the already identified solution, has it been validated and is the problem distinct from the analysis and potential solution, or have we leaked into the process.</t>
+          <t>Review Definitions: Review Semantic and Functional Definitions, ensuring there is sufficient and appropriate coverage. Testing and decisioning to occur during Feature Selection.</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -6266,184 +6286,185 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
-        <is>
-          <t>Stakeholder Investment?: How Invested are stakeholders in defining the problem? What is their view of the process/ project, how invested, interested and engaged are they. What are their personal goals and motivation, speed, accuracy, validation of ideology?</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Guidance</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>Really Understand Problem Statement: Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk and the likelihood of not meeting expectations, frustration, or material change to purpose, scope or priority is inevitable.</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Data Collection</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
-Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Guidance</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Data Collection</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Challenges from Missing Data: What concessions have we made due to a lack of data availability, and how are those going to undermine the work we plan on doing. </t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Guidance</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Data Collection</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>Who is the Steward: Who is the Data Steward, are they involved, and operationally do we have integrity, consistency and availability to include?</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Guidance</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Data Collection</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>Review Definitions: Review Semantic and Functional Definitions, ensuring there is sufficient and appropriate coverage. Testing and decisioning to occur during Feature Selection.</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Data Preparation</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
         <is>
           <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
 Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
 Where operational changes are necessary, or a prerequisite, need to understand how these will documented and escalated or addressed.</t>
         </is>
       </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Function cleans, reshapes, filters, joins, or transforms data into usable form.</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Baseline: Baseline represents the typical or expected behavior of an entity over a meaningful historical period. It answers the question “What is normal for this entity?” and provides context against which current state and changes can be interpreted. Baseline is conceptually stable even when its numeric value evolves, allowing models to distinguish structural differences between entities from temporary deviations. In modeling, Baseline is often foundational for defining identity and long-term segmentation.</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Baseline: Baseline represents the typical or expected behavior of an entity over a meaningful historical period. It answers the question “What is normal for this entity?” and provides context against which current state and changes can be interpreted. Baseline is conceptually stable even when its numeric value evolves, allowing models to distinguish structural differences between entities from temporary deviations. In modeling, Baseline is often foundational for defining identity and long-term segmentation.</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Dimension: A Dimension is a conceptual axis of behavior or meaning that you believe exists in the real world and want your model to represent. It answers a behavioral or semantic question, not a technical one. Dimensions are stable over time, even as data sources, features, or models change (for example, we always need to understand Current State, and rate of change, even though both of what is being studied may change drastically). They are the why behind your features.
+Ultimately, it is the question, What Behaviour Matters.</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Dimension: A Dimension is a conceptual axis of behavior or meaning that you believe exists in the real world and want your model to represent. It answers a behavioral or semantic question, not a technical one. Dimensions are stable over time, even as data sources, features, or models change (for example, we always need to understand Current State, and rate of change, even though both of what is being studied may change drastically). They are the why behind your features.
+Ultimately, it is the question, What Behaviour Matters.</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Implementation: An Implementation is a specific measurable representation of a dimension, derived from available data. It answers the question: “How is this dimension measured in practice?” Implementations operationalize a dimension through a defined calculation, methodology, or analytical approach. While implementations may evolve as data quality, availability, or methodology improves, they should always map clearly back to a single dimension.</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -6458,7 +6479,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6468,7 +6489,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Function cleans, reshapes, filters, joins, or transforms data into usable form.</t>
+          <t>Implementation: An Implementation is a specific measurable representation of a dimension, derived from available data. It answers the question: “How is this dimension measured in practice?” Implementations operationalize a dimension through a defined calculation, methodology, or analytical approach. While implementations may evolve as data quality, availability, or methodology improves, they should always map clearly back to a single dimension.</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -6495,7 +6516,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Baseline: Baseline represents the typical or expected behavior of an entity over a meaningful historical period. It answers the question “What is normal for this entity?” and provides context against which current state and changes can be interpreted. Baseline is conceptually stable even when its numeric value evolves, allowing models to distinguish structural differences between entities from temporary deviations. In modeling, Baseline is often foundational for defining identity and long-term segmentation.</t>
+          <t>Momentum: Momentum represents the direction and rate of change in behavior over time. It answers the question “Is this entity increasing, decreasing, or remaining stable?” and captures transitional dynamics that are not visible from state or baseline alone. Momentum is critical for detecting emerging trends, shifts in behavior, and potential future movement between segments. In modeling, Momentum often explains why change is occurring rather than what the current condition is.</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -6522,7 +6543,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Baseline: Baseline represents the typical or expected behavior of an entity over a meaningful historical period. It answers the question “What is normal for this entity?” and provides context against which current state and changes can be interpreted. Baseline is conceptually stable even when its numeric value evolves, allowing models to distinguish structural differences between entities from temporary deviations. In modeling, Baseline is often foundational for defining identity and long-term segmentation.</t>
+          <t>Momentum: Momentum represents the direction and rate of change in behavior over time. It answers the question “Is this entity increasing, decreasing, or remaining stable?” and captures transitional dynamics that are not visible from state or baseline alone. Momentum is critical for detecting emerging trends, shifts in behavior, and potential future movement between segments. In modeling, Momentum often explains why change is occurring rather than what the current condition is.</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -6549,8 +6570,8 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Dimension: A Dimension is a conceptual axis of behavior or meaning that you believe exists in the real world and want your model to represent. It answers a behavioral or semantic question, not a technical one. Dimensions are stable over time, even as data sources, features, or models change (for example, we always need to understand Current State, and rate of change, even though both of what is being studied may change drastically). They are the why behind your features.
-Ultimately, it is the question, What Behaviour Matters.</t>
+          <t>Parameter: A Parameter is a tuning choice that controls how an implementation is calculated, without changing what it represents. Parameters affect sensitivity, smoothness, or scale, but not conceptual meaning. They are the knobs you turn during experimentation. Examples include Window length: 3M vs 6M vs 12M, Weighting scheme: equal vs exponential, Aggregation: mean vs median
+Ultimately it is the questions, How do we compute it.</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -6577,8 +6598,8 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Dimension: A Dimension is a conceptual axis of behavior or meaning that you believe exists in the real world and want your model to represent. It answers a behavioral or semantic question, not a technical one. Dimensions are stable over time, even as data sources, features, or models change (for example, we always need to understand Current State, and rate of change, even though both of what is being studied may change drastically). They are the why behind your features.
-Ultimately, it is the question, What Behaviour Matters.</t>
+          <t>Parameter: A Parameter is a tuning choice that controls how an implementation is calculated, without changing what it represents. Parameters affect sensitivity, smoothness, or scale, but not conceptual meaning. They are the knobs you turn during experimentation. Examples include Window length: 3M vs 6M vs 12M, Weighting scheme: equal vs exponential, Aggregation: mean vs median
+Ultimately it is the questions, How do we compute it.</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -6605,7 +6626,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Implementation: An Implementation is a specific measurable representation of a dimension, derived from available data. It answers the question: “How is this dimension measured in practice?” Implementations operationalize a dimension through a defined calculation, methodology, or analytical approach. While implementations may evolve as data quality, availability, or methodology improves, they should always map clearly back to a single dimension.</t>
+          <t>Volatility: Volatility represents the consistency or variability of behavior over time. It answers the question “How stable or predictable is this entity’s behavior?” and distinguishes steady patterns from irregular or erratic ones. Volatility provides important diagnostic context, helping differentiate sustained change from noise or one-off events. In modeling, Volatility is typically explanatory or risk-related rather than defining core identity.</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -6632,7 +6653,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Implementation: An Implementation is a specific measurable representation of a dimension, derived from available data. It answers the question: “How is this dimension measured in practice?” Implementations operationalize a dimension through a defined calculation, methodology, or analytical approach. While implementations may evolve as data quality, availability, or methodology improves, they should always map clearly back to a single dimension.</t>
+          <t>Volatility: Volatility represents the consistency or variability of behavior over time. It answers the question “How stable or predictable is this entity’s behavior?” and distinguishes steady patterns from irregular or erratic ones. Volatility provides important diagnostic context, helping differentiate sustained change from noise or one-off events. In modeling, Volatility is typically explanatory or risk-related rather than defining core identity.</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -6649,7 +6670,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Regularization</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -6659,7 +6680,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Momentum: Momentum represents the direction and rate of change in behavior over time. It answers the question “Is this entity increasing, decreasing, or remaining stable?” and captures transitional dynamics that are not visible from state or baseline alone. Momentum is critical for detecting emerging trends, shifts in behavior, and potential future movement between segments. In modeling, Momentum often explains why change is occurring rather than what the current condition is.</t>
+          <t>ElasticNet: Approach which combines L1 and L2 Regularization.</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -6676,7 +6697,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Regularization</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -6686,7 +6707,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Momentum: Momentum represents the direction and rate of change in behavior over time. It answers the question “Is this entity increasing, decreasing, or remaining stable?” and captures transitional dynamics that are not visible from state or baseline alone. Momentum is critical for detecting emerging trends, shifts in behavior, and potential future movement between segments. In modeling, Momentum often explains why change is occurring rather than what the current condition is.</t>
+          <t>ElasticNet: Approach which combines L1 and L2 Regularization.</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -6703,7 +6724,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Regularization</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -6713,8 +6734,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Parameter: A Parameter is a tuning choice that controls how an implementation is calculated, without changing what it represents. Parameters affect sensitivity, smoothness, or scale, but not conceptual meaning. They are the knobs you turn during experimentation. Examples include Window length: 3M vs 6M vs 12M, Weighting scheme: equal vs exponential, Aggregation: mean vs median
-Ultimately it is the questions, How do we compute it.</t>
+          <t>Lasso: Technique used to prevent overfitting by adding penalty term to loss function. Adds the absolute values of the coefficients as a penalty term. This leads to sparse models, as some coefficients become exactly zero</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -6731,7 +6751,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Regularization</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -6741,8 +6761,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Parameter: A Parameter is a tuning choice that controls how an implementation is calculated, without changing what it represents. Parameters affect sensitivity, smoothness, or scale, but not conceptual meaning. They are the knobs you turn during experimentation. Examples include Window length: 3M vs 6M vs 12M, Weighting scheme: equal vs exponential, Aggregation: mean vs median
-Ultimately it is the questions, How do we compute it.</t>
+          <t>Lasso: Technique used to prevent overfitting by adding penalty term to loss function. Adds the absolute values of the coefficients as a penalty term. This leads to sparse models, as some coefficients become exactly zero</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -6759,7 +6778,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Regularization</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -6769,7 +6788,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Volatility: Volatility represents the consistency or variability of behavior over time. It answers the question “How stable or predictable is this entity’s behavior?” and distinguishes steady patterns from irregular or erratic ones. Volatility provides important diagnostic context, helping differentiate sustained change from noise or one-off events. In modeling, Volatility is typically explanatory or risk-related rather than defining core identity.</t>
+          <t>Ridge: Technique used to prevent overfitting by adding penalty term to loss function. Adds the squared values of the coefficients as a penalty term. This increases the cost of larger parameters, encouraging the model to distribute parameters waiting This shrinks the coefficients but does not eliminate them.</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -6786,7 +6805,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Regularization</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -6796,7 +6815,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Volatility: Volatility represents the consistency or variability of behavior over time. It answers the question “How stable or predictable is this entity’s behavior?” and distinguishes steady patterns from irregular or erratic ones. Volatility provides important diagnostic context, helping differentiate sustained change from noise or one-off events. In modeling, Volatility is typically explanatory or risk-related rather than defining core identity.</t>
+          <t>Ridge: Technique used to prevent overfitting by adding penalty term to loss function. Adds the squared values of the coefficients as a penalty term. This increases the cost of larger parameters, encouraging the model to distribute parameters waiting This shrinks the coefficients but does not eliminate them.</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -6823,7 +6842,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>ElasticNet: Approach which combines L1 and L2 Regularization.</t>
+          <t xml:space="preserve">Imputation: </t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -6850,7 +6869,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>ElasticNet: Approach which combines L1 and L2 Regularization.</t>
+          <t xml:space="preserve">Imputation: </t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -6877,7 +6896,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Lasso: Technique used to prevent overfitting by adding penalty term to loss function. Adds the absolute values of the coefficients as a penalty term. This leads to sparse models, as some coefficients become exactly zero</t>
+          <t xml:space="preserve">Deletion: </t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -6904,7 +6923,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Lasso: Technique used to prevent overfitting by adding penalty term to loss function. Adds the absolute values of the coefficients as a penalty term. This leads to sparse models, as some coefficients become exactly zero</t>
+          <t xml:space="preserve">Deletion: </t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -6921,7 +6940,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Regularization</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -6931,7 +6950,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Ridge: Technique used to prevent overfitting by adding penalty term to loss function. Adds the squared values of the coefficients as a penalty term. This increases the cost of larger parameters, encouraging the model to distribute parameters waiting This shrinks the coefficients but does not eliminate them.</t>
+          <t>Standardization: Standardization transforms data so the feature has a mean of 0 and a standard deviation of 1, typically using z-scores. It is commonly used for regression, clustering, PCA, and algorithms that assume approximately normally distributed inputs or are sensitive to feature scale. Its strengths are preserving relative variation and improving comparability across variables with different units or magnitudes. Its weaknesses are sensitivity to outliers and poor performance on heavily skewed data distributions unless preprocessing, such as log transformation or robust scaling, is applied first.</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -6948,7 +6967,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Regularization</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -6958,7 +6977,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Ridge: Technique used to prevent overfitting by adding penalty term to loss function. Adds the squared values of the coefficients as a penalty term. This increases the cost of larger parameters, encouraging the model to distribute parameters waiting This shrinks the coefficients but does not eliminate them.</t>
+          <t>Standardization: Standardization transforms data so the feature has a mean of 0 and a standard deviation of 1, typically using z-scores. It is commonly used for regression, clustering, PCA, and algorithms that assume approximately normally distributed inputs or are sensitive to feature scale. Its strengths are preserving relative variation and improving comparability across variables with different units or magnitudes. Its weaknesses are sensitivity to outliers and poor performance on heavily skewed data distributions unless preprocessing, such as log transformation or robust scaling, is applied first.</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -6975,7 +6994,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Regularization</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -6985,7 +7004,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Imputation: </t>
+          <t xml:space="preserve">Regularization: </t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -7002,7 +7021,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Regularization</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7012,7 +7031,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Imputation: </t>
+          <t xml:space="preserve">Regularization: </t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -7029,7 +7048,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Regularization</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7039,7 +7058,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deletion: </t>
+          <t>Log Transformation: Log transformation converts data using a logarithmic function, most commonly log⁡(1+x)log(1+x), to compress large values and reduce right-skewed distributions. It is especially useful for financial, transactional, and count-based data where a small number of observations are much larger than the rest. Its strengths are reducing outlier influence, improving distribution shape, and helping many ML algorithms perform more consistently. Its main weaknesses are reduced interpretability and compression of large-value differences, and it is primarily used before modeling when features have heavy skew or exponential growth patterns.</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -7056,7 +7075,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Regularization</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -7066,7 +7085,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deletion: </t>
+          <t>Log Transformation: Log transformation converts data using a logarithmic function, most commonly log⁡(1+x)log(1+x), to compress large values and reduce right-skewed distributions. It is especially useful for financial, transactional, and count-based data where a small number of observations are much larger than the rest. Its strengths are reducing outlier influence, improving distribution shape, and helping many ML algorithms perform more consistently. Its main weaknesses are reduced interpretability and compression of large-value differences, and it is primarily used before modeling when features have heavy skew or exponential growth patterns.</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -7083,7 +7102,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -7093,7 +7112,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Standardization: Standardization transforms data so the feature has a mean of 0 and a standard deviation of 1, typically using z-scores. It is commonly used for regression, clustering, PCA, and algorithms that assume approximately normally distributed inputs or are sensitive to feature scale. Its strengths are preserving relative variation and improving comparability across variables with different units or magnitudes. Its weaknesses are sensitivity to outliers and poor performance on heavily skewed data distributions unless preprocessing, such as log transformation or robust scaling, is applied first.</t>
+          <t>Normalization (Min-Max Scaling): Normalization rescales values into a fixed range, typically 0 to 1, using the minimum and maximum values of the feature. It is useful when features must operate on comparable scales, especially for neural networks, distance-based models, and composite scoring systems. Its strengths are simplicity, interpretability, and preserving the relative ordering of observations. Its main weakness is high sensitivity to outliers, since extreme values can compress most observations into a narrow range, making it less suitable for heavily skewed financial data unless transformation is applied first.</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -7110,7 +7129,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -7120,7 +7139,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Standardization: Standardization transforms data so the feature has a mean of 0 and a standard deviation of 1, typically using z-scores. It is commonly used for regression, clustering, PCA, and algorithms that assume approximately normally distributed inputs or are sensitive to feature scale. Its strengths are preserving relative variation and improving comparability across variables with different units or magnitudes. Its weaknesses are sensitivity to outliers and poor performance on heavily skewed data distributions unless preprocessing, such as log transformation or robust scaling, is applied first.</t>
+          <t>Normalization (Min-Max Scaling): Normalization rescales values into a fixed range, typically 0 to 1, using the minimum and maximum values of the feature. It is useful when features must operate on comparable scales, especially for neural networks, distance-based models, and composite scoring systems. Its strengths are simplicity, interpretability, and preserving the relative ordering of observations. Its main weakness is high sensitivity to outliers, since extreme values can compress most observations into a narrow range, making it less suitable for heavily skewed financial data unless transformation is applied first.</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -7137,7 +7156,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -7147,7 +7166,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regularization: </t>
+          <t>Standardization (Z-Score Scaling): Standardization transforms data so the feature has a mean of 0 and a standard deviation of 1, typically using z-scores. It is commonly used for regression, clustering, PCA, and algorithms that assume approximately normally distributed inputs or are sensitive to feature scale. Its strengths are preserving relative variation and improving comparability across variables with different units or magnitudes. Its weaknesses are sensitivity to outliers and poor performance on heavily skewed data distributions unless preprocessing, such as log transformation or robust scaling, is applied first.</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -7164,7 +7183,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -7174,7 +7193,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regularization: </t>
+          <t>Standardization (Z-Score Scaling): Standardization transforms data so the feature has a mean of 0 and a standard deviation of 1, typically using z-scores. It is commonly used for regression, clustering, PCA, and algorithms that assume approximately normally distributed inputs or are sensitive to feature scale. Its strengths are preserving relative variation and improving comparability across variables with different units or magnitudes. Its weaknesses are sensitivity to outliers and poor performance on heavily skewed data distributions unless preprocessing, such as log transformation or robust scaling, is applied first.</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -7191,17 +7210,18 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Exploratory Data Analysis</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Log Transformation: Log transformation converts data using a logarithmic function, most commonly log⁡(1+x)log(1+x), to compress large values and reduce right-skewed distributions. It is especially useful for financial, transactional, and count-based data where a small number of observations are much larger than the rest. Its strengths are reducing outlier influence, improving distribution shape, and helping many ML algorithms perform more consistently. Its main weaknesses are reduced interpretability and compression of large-value differences, and it is primarily used before modeling when features have heavy skew or exponential growth patterns.</t>
+          <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
+While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -7218,17 +7238,17 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Log Transformation: Log transformation converts data using a logarithmic function, most commonly log⁡(1+x)log(1+x), to compress large values and reduce right-skewed distributions. It is especially useful for financial, transactional, and count-based data where a small number of observations are much larger than the rest. Its strengths are reducing outlier influence, improving distribution shape, and helping many ML algorithms perform more consistently. Its main weaknesses are reduced interpretability and compression of large-value differences, and it is primarily used before modeling when features have heavy skew or exponential growth patterns.</t>
+          <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -7245,17 +7265,17 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Normalization (Min-Max Scaling): Normalization rescales values into a fixed range, typically 0 to 1, using the minimum and maximum values of the feature. It is useful when features must operate on comparable scales, especially for neural networks, distance-based models, and composite scoring systems. Its strengths are simplicity, interpretability, and preserving the relative ordering of observations. Its main weakness is high sensitivity to outliers, since extreme values can compress most observations into a narrow range, making it less suitable for heavily skewed financial data unless transformation is applied first.</t>
+          <t xml:space="preserve">   Function creates derived variables, metrics, flags, or analytical features</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -7272,17 +7292,17 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Normalization (Min-Max Scaling): Normalization rescales values into a fixed range, typically 0 to 1, using the minimum and maximum values of the feature. It is useful when features must operate on comparable scales, especially for neural networks, distance-based models, and composite scoring systems. Its strengths are simplicity, interpretability, and preserving the relative ordering of observations. Its main weakness is high sensitivity to outliers, since extreme values can compress most observations into a narrow range, making it less suitable for heavily skewed financial data unless transformation is applied first.</t>
+          <t>Ratios or Observed Values: What ratios or proportions could better represent behavior than raw values? Many real-world patterns depend on relative size (e.g., debt-to-income, usage-to-capacity), so ratios often reveal signal that absolute values hide.</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -7299,17 +7319,17 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Standardization (Z-Score Scaling): Standardization transforms data so the feature has a mean of 0 and a standard deviation of 1, typically using z-scores. It is commonly used for regression, clustering, PCA, and algorithms that assume approximately normally distributed inputs or are sensitive to feature scale. Its strengths are preserving relative variation and improving comparability across variables with different units or magnitudes. Its weaknesses are sensitivity to outliers and poor performance on heavily skewed data distributions unless preprocessing, such as log transformation or robust scaling, is applied first.</t>
+          <t>Ratios or Observed Values: What ratios or proportions could better represent behavior than raw values? Many real-world patterns depend on relative size (e.g., debt-to-income, usage-to-capacity), so ratios often reveal signal that absolute values hide.</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -7326,17 +7346,17 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Standardization (Z-Score Scaling): Standardization transforms data so the feature has a mean of 0 and a standard deviation of 1, typically using z-scores. It is commonly used for regression, clustering, PCA, and algorithms that assume approximately normally distributed inputs or are sensitive to feature scale. Its strengths are preserving relative variation and improving comparability across variables with different units or magnitudes. Its weaknesses are sensitivity to outliers and poor performance on heavily skewed data distributions unless preprocessing, such as log transformation or robust scaling, is applied first.</t>
+          <t>Include Interactions: What combinations or interactions might reflect how factors work together? Some outcomes are driven by the interaction between variables (e.g., high balance and high transaction frequency), so combining features can expose relationships a model might miss.</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -7353,18 +7373,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Exploratory Data Analysis</t>
+          <t>Feature Engineering</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
-While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
+          <t>Include Interactions: What combinations or interactions might reflect how factors work together? Some outcomes are driven by the interaction between variables (e.g., high balance and high transaction frequency), so combining features can expose relationships a model might miss.</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -7381,7 +7400,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7391,7 +7410,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
+          <t>How does Time Impact?: What time-based changes or aggregates could capture trends or stability? Differences, growth rates, or rolling averages often reflect momentum or consistency, which are strong predictors of future behavior.</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -7408,7 +7427,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -7418,7 +7437,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Function creates derived variables, metrics, flags, or analytical features</t>
+          <t>How does Time Impact?: What time-based changes or aggregates could capture trends or stability? Differences, growth rates, or rolling averages often reflect momentum or consistency, which are strong predictors of future behavior.</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -7435,17 +7454,18 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Ratios or Observed Values: What ratios or proportions could better represent behavior than raw values? Many real-world patterns depend on relative size (e.g., debt-to-income, usage-to-capacity), so ratios often reveal signal that absolute values hide.</t>
+          <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
+It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -7462,19 +7482,15 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>Ratios or Observed Values: What ratios or proportions could better represent behavior than raw values? Many real-world patterns depend on relative size (e.g., debt-to-income, usage-to-capacity), so ratios often reveal signal that absolute values hide.</t>
-        </is>
-      </c>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -7489,17 +7505,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Include Interactions: What combinations or interactions might reflect how factors work together? Some outcomes are driven by the interaction between variables (e.g., high balance and high transaction frequency), so combining features can expose relationships a model might miss.</t>
+          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -7516,17 +7532,17 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Include Interactions: What combinations or interactions might reflect how factors work together? Some outcomes are driven by the interaction between variables (e.g., high balance and high transaction frequency), so combining features can expose relationships a model might miss.</t>
+          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -7543,17 +7559,17 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>How does Time Impact?: What time-based changes or aggregates could capture trends or stability? Differences, growth rates, or rolling averages often reflect momentum or consistency, which are strong predictors of future behavior.</t>
+          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -7570,17 +7586,18 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>How does Time Impact?: What time-based changes or aggregates could capture trends or stability? Differences, growth rates, or rolling averages often reflect momentum or consistency, which are strong predictors of future behavior.</t>
+          <t>Area Under the Curve: AUC (Area Under the Curve) measures a model’s ability to distinguish between classes by summarizing the performance of the ROC (Receiver Operating Characteristic) curve. It represents the probability that the model ranks a randomly chosen positive example higher than a randomly chosen negative one. AUC ranges from 0.5 (no better than chance) to 1.0 (perfect separation), with higher values indicating better classification performance.
+AUC is primarily a binary classification metric, so when using against a multivariate challenge must determine how to score, OVR, OVO. One Vs Rest, One vs One. Using MNist as an example, OVR evaluates 10 0 vs (1,2,3,4,5,6,7,8,9), 1 vs () ... etc, Where OVO measures 45 0 Vs 1, 0 vs 2, etc..</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -7597,210 +7614,209 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
-        <is>
-          <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
-It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Hyperparameter Tuning</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>Area Under the Curve: AUC (Area Under the Curve) measures a model’s ability to distinguish between classes by summarizing the performance of the ROC (Receiver Operating Characteristic) curve. It represents the probability that the model ranks a randomly chosen positive example higher than a randomly chosen negative one. AUC ranges from 0.5 (no better than chance) to 1.0 (perfect separation), with higher values indicating better classification performance.
-AUC is primarily a binary classification metric, so when using against a multivariate challenge must determine how to score, OVR, OVO. One Vs Rest, One vs One. Using MNist as an example, OVR evaluates 10 0 vs (1,2,3,4,5,6,7,8,9), 1 vs () ... etc, Where OVO measures 45 0 Vs 1, 0 vs 2, etc..</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
         <is>
           <t>Bias: Bias refers to the systematic error in a model that causes it to consistently deviate from the true value or correct predictions. It occurs when an algorithm makes incorrect assumptions or omissions about the data, leading to errors.
 High Bias (Underfitting): The model is too simple and cannot capture patterns. 
 Low Bias, High Variance (Overfitting). The model memorizes the data but does not generalize.</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
         <is>
           <t>Machine Learning Lifecycle</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
+      <c r="B274" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
+      <c r="C274" t="inlineStr">
         <is>
           <t>Model Evaluation</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr">
+      <c r="D274" t="inlineStr">
         <is>
           <t>Bias - Variance Trade Off: The bias-variance trade-off is a key concept in machine learning that highlights the balance between two sources of error: bias and variance, tuning the relationship between a model's complexity, the accuracy of its predictions, and how well it can make predictions on previously unseen data that were not used to train the model The challenge is to find a model that strikes the right balance between bias and variance, as reducing one typically increases the other. The ultimate goal is to minimize the total error, which is the sum of bias error, variance error, and irreducible noise inherent in the data. Achieving this balance ensures the model generalizes well to new, unseen data, avoiding both underfitting and overfitting. More Data vs More Data Science - Bias vs Variance 
 It can often be explained by the Trade-Off (Bias - Data Scientist, Variance - Data), where to invest.
 In general, as we increase the number of tunable parameters in a model, it becomes more flexible, and can better fit a training data set. It is said to have lower error, or bias. However, for more flexible models, there will tend to be greater variance to the model fit each time we take a set of samples to create a new training data set. It is said that there is greater variance in the model's estimated parameters.High-variance learning methods may be able to represent their training set well but are at risk of overfitting to noisy or unrepresentative training data. In contrast, algorithms with high bias typically produce simpler models that may fail to capture important regularities (i.e. underfit) in the data.</t>
         </is>
       </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Variance: Variance refers to errors caused by models that are too sensitive to small fluctuations in the training data, often resulting in overfitting. High-variance models are overly flexible, capturing noise as if it were meaningful patterns. A model with many degrees of freedom (such as a high-degree polynomial model) is likely to have high variance and thus overfit the training data. As an example, if you created a model of How Predicting Housing Prices in 1 Neighbourhood would work and applied it to different neighbourhoods, if your model was simple, it wouldn't work well anywhere and thus would be Wrong, but consistently-ish wrong. If your model was Good, it would work similarly well every well. If you model was overfit, it would work really well in 1 place, not so well elsewhere.
+</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -7815,18 +7831,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>General Definition</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Variance: Variance refers to errors caused by models that are too sensitive to small fluctuations in the training data, often resulting in overfitting. High-variance models are overly flexible, capturing noise as if it were meaningful patterns. A model with many degrees of freedom (such as a high-degree polynomial model) is likely to have high variance and thus overfit the training data. As an example, if you created a model of How Predicting Housing Prices in 1 Neighbourhood would work and applied it to different neighbourhoods, if your model was simple, it wouldn't work well anywhere and thus would be Wrong, but consistently-ish wrong. If your model was Good, it would work similarly well every well. If you model was overfit, it would work really well in 1 place, not so well elsewhere.
-</t>
+          <t>Heirarchal Structure to guide for a robust and successful Machine Learning Project, including all of the high level steps/consideration which must be given.</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -7838,22 +7853,23 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Area Under the Curve</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
+          <t>AUC (Area Under the Curve) measures a model’s ability to distinguish between classes by summarizing the performance of the ROC (Receiver Operating Characteristic) curve. It represents the probability that the model ranks a randomly chosen positive example higher than a randomly chosen negative one. AUC ranges from 0.5 (no better than chance) to 1.0 (perfect separation), with higher values indicating better classification performance.
+AUC is primarily a binary classification metric, so when using against a multivariate challenge must determine how to score, OVR, OVO. One Vs Rest, One vs One. Using MNist as an example, OVR evaluates 10 0 vs (1,2,3,4,5,6,7,8,9), 1 vs () ... etc, Where OVO measures 45 0 Vs 1, 0 vs 2, etc..</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -7865,214 +7881,218 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr"/>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>Deployment</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
-        </is>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Bias, Fairness, and Ethics</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
-        </is>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>Heirarchal Structure to guide for a robust and successful Machine Learning Project, including all of the high level steps/consideration which must be given.</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>Area Under the Curve</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>AUC (Area Under the Curve) measures a model’s ability to distinguish between classes by summarizing the performance of the ROC (Receiver Operating Characteristic) curve. It represents the probability that the model ranks a randomly chosen positive example higher than a randomly chosen negative one. AUC ranges from 0.5 (no better than chance) to 1.0 (perfect separation), with higher values indicating better classification performance.
-AUC is primarily a binary classification metric, so when using against a multivariate challenge must determine how to score, OVR, OVO. One Vs Rest, One vs One. Using MNist as an example, OVR evaluates 10 0 vs (1,2,3,4,5,6,7,8,9), 1 vs () ... etc, Where OVO measures 45 0 Vs 1, 0 vs 2, etc..</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>Feature Selection</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr">
+      <c r="D283" t="inlineStr">
         <is>
           <t>Bias refers to the systematic error in a model that causes it to consistently deviate from the true value or correct predictions. It occurs when an algorithm makes incorrect assumptions or omissions about the data, leading to errors.
 High Bias (Underfitting): The model is too simple and cannot capture patterns. 
 Low Bias, High Variance (Overfitting). The model memorizes the data but does not generalize.</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>Knowledge Base</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
         <is>
           <t>Model Evaluation</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
+      <c r="B284" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr">
+      <c r="C284" t="inlineStr">
         <is>
           <t>Bias - Variance Trade Off</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr">
+      <c r="D284" t="inlineStr">
         <is>
           <t>The bias-variance trade-off is a key concept in machine learning that highlights the balance between two sources of error: bias and variance, tuning the relationship between a model's complexity, the accuracy of its predictions, and how well it can make predictions on previously unseen data that were not used to train the model The challenge is to find a model that strikes the right balance between bias and variance, as reducing one typically increases the other. The ultimate goal is to minimize the total error, which is the sum of bias error, variance error, and irreducible noise inherent in the data. Achieving this balance ensures the model generalizes well to new, unseen data, avoiding both underfitting and overfitting. More Data vs More Data Science - Bias vs Variance 
 It can often be explained by the Trade-Off (Bias - Data Scientist, Variance - Data), where to invest.
 In general, as we increase the number of tunable parameters in a model, it becomes more flexible, and can better fit a training data set. It is said to have lower error, or bias. However, for more flexible models, there will tend to be greater variance to the model fit each time we take a set of samples to create a new training data set. It is said that there is greater variance in the model's estimated parameters.High-variance learning methods may be able to represent their training set well but are at risk of overfitting to noisy or unrepresentative training data. In contrast, algorithms with high bias typically produce simpler models that may fail to capture important regularities (i.e. underfit) in the data.</t>
         </is>
       </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Variance</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Variance refers to errors caused by models that are too sensitive to small fluctuations in the training data, often resulting in overfitting. High-variance models are overly flexible, capturing noise as if it were meaningful patterns. A model with many degrees of freedom (such as a high-degree polynomial model) is likely to have high variance and thus overfit the training data. As an example, if you created a model of How Predicting Housing Prices in 1 Neighbourhood would work and applied it to different neighbourhoods, if your model was simple, it wouldn't work well anywhere and thus would be Wrong, but consistently-ish wrong. If your model was Good, it would work similarly well every well. If you model was overfit, it would work really well in 1 place, not so well elsewhere.
+</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Baseline Metrics (Current State)</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Current State Analysis</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Desired State Metrics</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Historical Overview</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Knowledge Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Really Understand Problem Statement</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk and the likelihood of not meeting expectations, frustration, or material change to purpose, scope or priority is inevitable.</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -8082,23 +8102,22 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Variance</t>
+          <t>Root Cause Assessment</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Variance refers to errors caused by models that are too sensitive to small fluctuations in the training data, often resulting in overfitting. High-variance models are overly flexible, capturing noise as if it were meaningful patterns. A model with many degrees of freedom (such as a high-degree polynomial model) is likely to have high variance and thus overfit the training data. As an example, if you created a model of How Predicting Housing Prices in 1 Neighbourhood would work and applied it to different neighbourhoods, if your model was simple, it wouldn't work well anywhere and thus would be Wrong, but consistently-ish wrong. If your model was Good, it would work similarly well every well. If you model was overfit, it would work really well in 1 place, not so well elsewhere.
-</t>
+          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -8115,17 +8134,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Baseline Metrics (Current State)</t>
+          <t>Stakeholder Investment?</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+          <t>How Invested are stakeholders in defining the problem? What is their view of the process/ project, how invested, interested and engaged are they. What are their personal goals and motivation, speed, accuracy, validation of ideology?</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -8142,17 +8161,18 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Current State Analysis</t>
+          <t>Understand KPIs which are meaningful.</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+          <t>Attempt to explicitly define outcomes and relevant KPIs for those outcomes. Where that can not happen, it is important to understand why that can not happen. What is happening if we don't have and follow metrics. IE. The Account Opening Process is not efficient and needs to improve, The Internet Banking Experience is poor, and does not attract customers. How do you monitor this, how can you define this, how can you prove this,  how do you expect this to change and measure that change.
+How will the project and efforts be measured where success can not be objectively measured? How will resources be allocated when it remains unclear what benefit or risk exists.</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -8169,17 +8189,17 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Desired State Metrics</t>
+          <t>What Lens is Problem Defined?</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+          <t>Must be careful at how problem is defined. Is it defined in the context of the already identified solution, has it been validated and is the problem distinct from the analysis and potential solution, or have we leaked into the process.</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -8191,7 +8211,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -8201,12 +8221,12 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Historical Overview</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -8218,22 +8238,22 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Really Understand Problem Statement</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk and the likelihood of not meeting expectations, frustration, or material change to purpose, scope or priority is inevitable.</t>
+          <t>Specific: Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -8245,22 +8265,22 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Root Cause Assessment</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+          <t>Measurable: Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -8272,22 +8292,22 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Stakeholder Investment?</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>How Invested are stakeholders in defining the problem? What is their view of the process/ project, how invested, interested and engaged are they. What are their personal goals and motivation, speed, accuracy, validation of ideology?</t>
+          <t>Achievable: Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -8299,23 +8319,22 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Understand KPIs which are meaningful.</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Attempt to explicitly define outcomes and relevant KPIs for those outcomes. Where that can not happen, it is important to understand why that can not happen. What is happening if we don't have and follow metrics. IE. The Account Opening Process is not efficient and needs to improve, The Internet Banking Experience is poor, and does not attract customers. How do you monitor this, how can you define this, how can you prove this,  how do you expect this to change and measure that change.
-How will the project and efforts be measured where success can not be objectively measured? How will resources be allocated when it remains unclear what benefit or risk exists.</t>
+          <t>Relevant: Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -8327,22 +8346,22 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>What Lens is Problem Defined?</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Must be careful at how problem is defined. Is it defined in the context of the already identified solution, has it been validated and is the problem distinct from the analysis and potential solution, or have we leaked into the process.</t>
+          <t>Time Bound: Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -8364,12 +8383,12 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -8386,17 +8405,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Specific: Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
+          <t>Desired State Metrics: Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -8413,17 +8432,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Measurable: Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
+          <t>Current State Analysis: Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -8440,17 +8459,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Achievable: Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
+          <t>Root Cause Assessment: Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -8467,17 +8486,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Relevant: Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
+          <t>Historical Overview: Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -8494,17 +8513,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Time Bound: Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
+          <t>Baseline Metrics (Current State): Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -8521,7 +8540,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -8531,7 +8550,8 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+          <t>Understand KPIs which are meaningful.: Attempt to explicitly define outcomes and relevant KPIs for those outcomes. Where that can not happen, it is important to understand why that can not happen. What is happening if we don't have and follow metrics. IE. The Account Opening Process is not efficient and needs to improve, The Internet Banking Experience is poor, and does not attract customers. How do you monitor this, how can you define this, how can you prove this,  how do you expect this to change and measure that change.
+How will the project and efforts be measured where success can not be objectively measured? How will resources be allocated when it remains unclear what benefit or risk exists.</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -8548,7 +8568,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -8558,7 +8578,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Desired State Metrics: Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+          <t>What Lens is Problem Defined?: Must be careful at how problem is defined. Is it defined in the context of the already identified solution, has it been validated and is the problem distinct from the analysis and potential solution, or have we leaked into the process.</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -8575,7 +8595,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -8585,7 +8605,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Current State Analysis: Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+          <t>Stakeholder Investment?: How Invested are stakeholders in defining the problem? What is their view of the process/ project, how invested, interested and engaged are they. What are their personal goals and motivation, speed, accuracy, validation of ideology?</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -8602,7 +8622,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -8612,7 +8632,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Root Cause Assessment: Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+          <t>Really Understand Problem Statement: Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk and the likelihood of not meeting expectations, frustration, or material change to purpose, scope or priority is inevitable.</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -8634,14 +8654,10 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>Historical Overview: Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
-        </is>
-      </c>
+          <t>Current State Assessment</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -8661,12 +8677,13 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Baseline Metrics (Current State): Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+          <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
+Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -8688,13 +8705,12 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Understand KPIs which are meaningful.: Attempt to explicitly define outcomes and relevant KPIs for those outcomes. Where that can not happen, it is important to understand why that can not happen. What is happening if we don't have and follow metrics. IE. The Account Opening Process is not efficient and needs to improve, The Internet Banking Experience is poor, and does not attract customers. How do you monitor this, how can you define this, how can you prove this,  how do you expect this to change and measure that change.
-How will the project and efforts be measured where success can not be objectively measured? How will resources be allocated when it remains unclear what benefit or risk exists.</t>
+          <t xml:space="preserve">Challenges from Missing Data: What concessions have we made due to a lack of data availability, and how are those going to undermine the work we plan on doing. </t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -8716,12 +8732,12 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>What Lens is Problem Defined?: Must be careful at how problem is defined. Is it defined in the context of the already identified solution, has it been validated and is the problem distinct from the analysis and potential solution, or have we leaked into the process.</t>
+          <t>Who is the Steward: Who is the Data Steward, are they involved, and operationally do we have integrity, consistency and availability to include?</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -8743,12 +8759,12 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Stakeholder Investment?: How Invested are stakeholders in defining the problem? What is their view of the process/ project, how invested, interested and engaged are they. What are their personal goals and motivation, speed, accuracy, validation of ideology?</t>
+          <t>Review Definitions: Review Semantic and Functional Definitions, ensuring there is sufficient and appropriate coverage. Testing and decisioning to occur during Feature Selection.</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -8765,19 +8781,15 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>Really Understand Problem Statement: Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk and the likelihood of not meeting expectations, frustration, or material change to purpose, scope or priority is inevitable.</t>
-        </is>
-      </c>
+          <t>Root Cause Analysis</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -8797,7 +8809,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Current State Assessment</t>
+          <t>Research and Exploration</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -8820,15 +8832,10 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Data Collection</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
-Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
-        </is>
-      </c>
+          <t>Option Generation</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -8843,19 +8850,15 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Data Collection</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Challenges from Missing Data: What concessions have we made due to a lack of data availability, and how are those going to undermine the work we plan on doing. </t>
-        </is>
-      </c>
+          <t>Solution Design</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -8870,19 +8873,15 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Data Collection</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>Who is the Steward: Who is the Data Steward, are they involved, and operationally do we have integrity, consistency and availability to include?</t>
-        </is>
-      </c>
+          <t>Feasibility Assessment</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -8897,19 +8896,15 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Data Collection</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>Review Definitions: Review Semantic and Functional Definitions, ensuring there is sufficient and appropriate coverage. Testing and decisioning to occur during Feature Selection.</t>
-        </is>
-      </c>
+          <t>Prioritization and Decision Making</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -8929,7 +8924,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Root Cause Analysis</t>
+          <t>Implementation Planning</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -8952,7 +8947,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Research and Exploration</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -8975,7 +8970,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Option Generation</t>
+          <t>Testing and Validation</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -8998,7 +8993,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Solution Design</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -9021,7 +9016,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Feasibility Assessment</t>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
@@ -9044,7 +9039,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Prioritization and Decision Making</t>
+          <t>Documentation and Knowledge Sharing</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
@@ -9067,10 +9062,14 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Implementation Planning</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -9090,7 +9089,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Continuous Improvement</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
@@ -9113,7 +9112,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Testing and Validation</t>
+          <t>Governance, Risk, and Ethics</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
@@ -9131,15 +9130,19 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Evaluation</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Structured approach to solving complex problems.</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>Knowledge Base</t>
@@ -9149,146 +9152,138 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Optimization</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Knowledge Base</t>
+          <t>Manual Objects</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Documentation and Knowledge Sharing</t>
+          <t>Parameters</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Knowledge Base</t>
+          <t>Manual Objects</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
-        </is>
-      </c>
+          <t>Returns</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Knowledge Base</t>
+          <t>Manual Objects</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Continuous Improvement</t>
+          <t>Date Created</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Knowledge Base</t>
+          <t>Manual Objects</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Governance, Risk, and Ethics</t>
+          <t>Date Last Modified</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Knowledge Base</t>
+          <t>Manual Objects</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Default Python String Taxonomy</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>Structured approach to solving complex problems.</t>
-        </is>
-      </c>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Knowledge Base</t>
+          <t>Manual Objects</t>
         </is>
       </c>
     </row>
@@ -9305,7 +9300,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Categorization</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
@@ -9328,7 +9323,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Parameters</t>
+          <t>Usage</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
@@ -9351,7 +9346,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Returns</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -9369,15 +9364,19 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Date Created</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Default Columns to be included and labelled when documenting personally created functions in Python</t>
+        </is>
+      </c>
       <c r="E341" t="inlineStr">
         <is>
           <t>Manual Objects</t>
@@ -9387,17 +9386,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Default Python String Taxonomy</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Date Last Modified</t>
+          <t>Homoscedasticity</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
@@ -9410,17 +9409,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Default Python String Taxonomy</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Independence</t>
         </is>
       </c>
       <c r="D343" t="inlineStr"/>
@@ -9433,17 +9432,17 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Default Python String Taxonomy</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Categorization</t>
+          <t>Linearity</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
@@ -9456,17 +9455,17 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Default Python String Taxonomy</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Usage</t>
+          <t>Normality</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
@@ -9479,20 +9478,24 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Default Python String Taxonomy</t>
+          <t>Best Linear Unbiased Estimator</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>The Best Linear Unbiased Estimator (BLUE) is an estimation method in statistics that produces parameter estimates that are linear in the observed data, unbiased, and have the smallest possible variance among all such estimators. It originates from the Gauss–Markov theorem, developed in the early 19th century in the context of least squares and error theory. Its importance lies in providing a theoretical benchmark: under specific assumptions about error structure, no other linear unbiased estimator can be more precise. In practice, BLUE underpins ordinary and generalized least squares, and is widely applied in econometrics, engineering, and data science when modeling relationships with correlated or heteroskedastic errors</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>Manual Objects</t>
@@ -9502,24 +9505,20 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Default Python String Taxonomy</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>Default Columns to be included and labelled when documenting personally created functions in Python</t>
-        </is>
-      </c>
+          <t>Process Definition</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
           <t>Manual Objects</t>
@@ -9529,17 +9528,17 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Best Linear Unbiased Estimator</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Homoscedasticity</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
@@ -9552,17 +9551,17 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Best Linear Unbiased Estimator</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Independence</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
@@ -9575,17 +9574,17 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Best Linear Unbiased Estimator</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Linearity</t>
+          <t>Guiding Principle</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
@@ -9598,17 +9597,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Best Linear Unbiased Estimator</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Normality</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
@@ -9621,24 +9620,20 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Best Linear Unbiased Estimator</t>
+          <t>Categorization Filter Order</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Filter Order</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>The Best Linear Unbiased Estimator (BLUE) is an estimation method in statistics that produces parameter estimates that are linear in the observed data, unbiased, and have the smallest possible variance among all such estimators. It originates from the Gauss–Markov theorem, developed in the early 19th century in the context of least squares and error theory. Its importance lies in providing a theoretical benchmark: under specific assumptions about error structure, no other linear unbiased estimator can be more precise. In practice, BLUE underpins ordinary and generalized least squares, and is widely applied in econometrics, engineering, and data science when modeling relationships with correlated or heteroskedastic errors</t>
-        </is>
-      </c>
+          <t>Expected Outcomes</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
           <t>Manual Objects</t>
@@ -9658,7 +9653,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Process Definition</t>
+          <t>Parameter</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -9681,7 +9676,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Algorithm</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
@@ -9704,7 +9699,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
@@ -9722,15 +9717,19 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Guiding Principle</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Default Column Order to be applied while filtering Notes to D Knowledge Base or/and D Processes</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>Manual Objects</t>
@@ -9740,17 +9739,17 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Categorization Filter Order</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
@@ -9763,17 +9762,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Categorization Filter Order</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Expected Outcomes</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
@@ -9786,17 +9785,17 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Categorization Filter Order</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Parameter</t>
+          <t>Current State Assessment</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
@@ -9809,17 +9808,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Categorization Filter Order</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Algorithm</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
@@ -9832,17 +9831,17 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Categorization Filter Order</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Filter Order</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Root Cause Analysis</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
@@ -9855,24 +9854,20 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Categorization Filter Order</t>
+          <t>Problem Solving Framework</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>Default Column Order to be applied while filtering Notes to D Knowledge Base or/and D Processes</t>
-        </is>
-      </c>
+          <t>Research and Exploration</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
           <t>Manual Objects</t>
@@ -9892,7 +9887,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Option Generation</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -9915,7 +9910,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Solution Design</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -9938,7 +9933,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Current State Assessment</t>
+          <t>Feasibility Assessment</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -9961,7 +9956,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Data Collection</t>
+          <t>Prioritization and Decision Making</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -9984,7 +9979,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Root Cause Analysis</t>
+          <t>Implementation Planning</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -10007,7 +10002,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Research and Exploration</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -10030,7 +10025,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Option Generation</t>
+          <t>Testing and Validation</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -10053,7 +10048,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Solution Design</t>
+          <t>Evaluation</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -10076,7 +10071,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Feasibility Assessment</t>
+          <t>Optimization</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
@@ -10099,7 +10094,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Prioritization and Decision Making</t>
+          <t>Documentation and Knowledge Sharing</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
@@ -10122,7 +10117,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Implementation Planning</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
@@ -10145,7 +10140,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Continuous Improvement</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -10168,7 +10163,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Testing and Validation</t>
+          <t>Governance, Risk, and Ethics</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -10186,15 +10181,19 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Evaluation</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Structured approach to solving complex problems.</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>Manual Objects</t>
@@ -10204,7 +10203,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -10214,7 +10213,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Optimization</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -10227,7 +10226,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -10237,7 +10236,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Documentation and Knowledge Sharing</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
@@ -10250,7 +10249,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -10260,7 +10259,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Data Collection</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -10273,7 +10272,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -10283,7 +10282,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Continuous Improvement</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -10296,7 +10295,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -10306,7 +10305,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Governance, Risk, and Ethics</t>
+          <t>Exploratory Data Analysis</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -10319,24 +10318,20 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Problem Solving Framework</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>Structured approach to solving complex problems.</t>
-        </is>
-      </c>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr">
         <is>
           <t>Manual Objects</t>
@@ -10356,7 +10351,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Feature Selection</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -10379,7 +10374,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Model Selection</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -10402,7 +10397,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Data Collection</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -10425,7 +10420,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Data Preparation</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -10448,7 +10443,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Exploratory Data Analysis</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -10471,7 +10466,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Feature Engineering</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -10494,7 +10489,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Feature Selection</t>
+          <t>Model Interpretability</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -10517,7 +10512,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Model Selection</t>
+          <t>Deployment</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -10540,7 +10535,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -10563,7 +10558,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
+          <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -10581,15 +10576,19 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Heirarchal Structure to guide for a robust and successful Machine Learning Project, including all of the high level steps/consideration which must be given.</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>Manual Objects</t>
@@ -10599,17 +10598,17 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>FINALNAME</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
@@ -10622,17 +10621,17 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
+          <t>COLUMN</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -10645,17 +10644,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>METRIC_TYPE</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -10668,17 +10667,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>METRIC_CLASSIFICATION</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -10691,17 +10690,17 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
+          <t>PRODUCT</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -10714,24 +10713,20 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Data Dictionary Columns</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Reference List</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>Heirarchal Structure to guide for a robust and successful Machine Learning Project, including all of the high level steps/consideration which must be given.</t>
-        </is>
-      </c>
+          <t>DESCRIPTION</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr">
         <is>
           <t>Manual Objects</t>
@@ -10751,7 +10746,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>FINALNAME</t>
+          <t>METRIC</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -10774,7 +10769,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>COLUMN</t>
+          <t>NOTES</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
@@ -10797,7 +10792,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>METRIC_TYPE</t>
+          <t>RECORD_TYPE</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -10820,7 +10815,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>METRIC_CLASSIFICATION</t>
+          <t>UPDATE_DATE</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -10838,158 +10833,20 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Reference List</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>PRODUCT</t>
-        </is>
-      </c>
-      <c r="D404" t="inlineStr"/>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>List of Default Columns Used in Data Dictionary</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
-        <is>
-          <t>Manual Objects</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>Data Dictionary Columns</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr"/>
-      <c r="E405" t="inlineStr">
-        <is>
-          <t>Manual Objects</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>Data Dictionary Columns</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>METRIC</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr"/>
-      <c r="E406" t="inlineStr">
-        <is>
-          <t>Manual Objects</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>Data Dictionary Columns</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr"/>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>Manual Objects</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>Data Dictionary Columns</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>RECORD_TYPE</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr"/>
-      <c r="E408" t="inlineStr">
-        <is>
-          <t>Manual Objects</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>Data Dictionary Columns</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>Reference List</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>UPDATE_DATE</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr"/>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>Manual Objects</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>Data Dictionary Columns</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>List of Default Columns Used in Data Dictionary</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr">
         <is>
           <t>Manual Objects</t>
         </is>

--- a/Streamlit/Data/consolidated_dataset.xlsx
+++ b/Streamlit/Data/consolidated_dataset.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,21 +437,6 @@
           <t>Definition</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>NP_ORDER</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>CAT_ORDER</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PROC_ORDER</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -474,11 +459,6 @@
           <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -502,11 +482,6 @@
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -531,11 +506,6 @@
 Where operational changes are necessary, or a prerequisite, need to understand how these will documented and escalated or addressed.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -558,11 +528,6 @@
           <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -586,11 +551,6 @@
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -613,11 +573,6 @@
           <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -641,11 +596,6 @@
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -668,11 +618,6 @@
           <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -695,11 +640,6 @@
           <t>Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>30</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,11 +662,6 @@
           <t>Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>31</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -749,11 +684,6 @@
           <t>Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>32</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -776,11 +706,6 @@
           <t>Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>33</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -803,11 +728,6 @@
           <t>Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>34</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -830,11 +750,6 @@
           <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -857,15 +772,6 @@
           <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>14</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -888,13 +794,6 @@
           <t>Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>30</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -917,13 +816,6 @@
           <t>Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>31</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -946,13 +838,6 @@
           <t>Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>32</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -975,13 +860,6 @@
           <t>Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>33</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1004,13 +882,6 @@
           <t>Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>34</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1033,15 +904,6 @@
           <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>15</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1064,15 +926,6 @@
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
-      </c>
-      <c r="E23" t="n">
-        <v>16</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1098,15 +951,6 @@
 Where operational changes are necessary, or a prerequisite, need to understand how these will documented and escalated or addressed.</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>17</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1130,15 +974,6 @@
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>18</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1161,15 +996,6 @@
           <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>19</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1193,15 +1019,6 @@
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>20</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1224,15 +1041,6 @@
           <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>22</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>8</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1255,15 +1063,6 @@
           <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>23</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1286,15 +1085,6 @@
           <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>24</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="n">
-        <v>10</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1317,15 +1107,6 @@
           <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>25</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="n">
-        <v>11</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1348,15 +1129,6 @@
           <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>27</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="n">
-        <v>13</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1379,15 +1151,6 @@
           <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>28</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="n">
-        <v>14</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1410,15 +1173,6 @@
           <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>29</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1441,11 +1195,6 @@
           <t>To Be Defined</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1464,13 +1213,6 @@
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
-        <v>21</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1489,13 +1231,6 @@
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
-        <v>26</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1518,11 +1253,6 @@
           <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1545,11 +1275,6 @@
           <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1572,11 +1297,6 @@
           <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1599,11 +1319,6 @@
           <t>List used to manage the default order of items as stored in the Notes Sheet. Specifically, there is a heirarchical order created and expected to prioritize how items are stored and filter, this list maintains that order and can be used as guidance to understand.</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1626,11 +1341,6 @@
           <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1653,11 +1363,6 @@
           <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1680,11 +1385,6 @@
           <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1708,11 +1408,6 @@
 Similar to the process of engagement and audit followed in Feature Selection, it is critically important that actions are documented, defensible and clearly and consistently articulated to stakeholders in a meaningful manner.</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Streamlit/Data/consolidated_dataset.xlsx
+++ b/Streamlit/Data/consolidated_dataset.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,65 +441,376 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
+          <t>Behavioural Economics</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Anchoring Effect</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+          <t>A cognitive bias where people rely too heavily on the first piece of information (the “anchor”) when making decisions. Once an anchor is set, it influences subsequent judgments, even if it’s arbitrary or unrelated. For example, when asked whether the Eiffel Tower is taller or shorter than 500 feet, people’s estimates will cluster around that number. This bias can affect pricing, negotiations, and even forecasting.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Base Rate Fallacy</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>People ignore or undervalue general statistical information (the base rate) and focus instead on specific information, often leading to incorrect conclusions. In decision-making, individuals may give more weight to anecdotal or vivid information, despite the broader statistical reality that should influence their judgment. Imagine a test for a rare disease that is 95% accurate. The disease affects 1 in 10,000 people. If a person tests positive, many might assume the likelihood of them having the disease is high. However, considering the base rate (the rarity of the disease), the probability of actually having the disease is still very low. In this scenario, the base rate fallacy would be ignoring the low prevalence of the disease (the base rate) and overestimating the accuracy of the test result, leading to an exaggerated belief in the likelihood of the person having the disease. The fallacy demonstrates how people's intuitive reasoning often neglects the significance of background statistical data in favor of more attention-grabbing or salient information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bureaucratic Politics</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Organization decision making paradigm in which decisions are made based solely on who is making the decision, specifically, they will decide in their own best interests. Counters prevalent theory in which a rational, fair or logical decision making process will occur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Biased Assimilation</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tendency to interpret information in a way that supports a desired conclusion. </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Blind spot bias</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Cognitive bias where people are unaware of their own biases, while easily recognizing the biases in others.  People tend to believe they are more objective, rational, and less susceptible to biases than others, even though they may exhibit the same biases in their own thinking. Self-awareness gap: People can easily identify cognitive biases (like confirmation bias, motivated reasoning, or stereotyping) in others, but fail to recognize these biases in themselves. Overconfidence in objectivity: Individuals often overestimate their own ability to reason without bias, which can lead to an inflated sense of confidence in their decisions and beliefs. Resistance to feedback: Blind spot bias can make people resistant to feedback, because they believe that they’re viewing situations or information more objectively than they actually are.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Confirmation Bias</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Also known as Selective Perception. What people see can be strongly shaped by what they believe, using the example of a study which occurred during a especially dirty Princeton Dartmouth Football game. After the game people were asked to comment which team was "Dirtier" and results were based on which team individuals had allegiance with.
+Tendency to search for, interpret, and remember information in a way that confirms one’s preexisting beliefs or hypotheses. People often ignore or downplay evidence that contradicts their views. This bias can reinforce stereotypes, polarize opinions, and skew data interpretation. It’s especially important to watch for in research, media consumption, and decision-making.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fast statistics </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Immoderate, intuitive, visceral, and powerful.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Slow statistics</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Thoughtful gathering of unbiased information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Truth-default theory </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>54% accurate identifying liar. We can identify truth tellers far more easily, bad at identifying liars. We start in a default position of believing people and only when substantial evidence to the contrary presents itself do we change our position. In fact, we can even trivialize information away that in hindsight it rather pertinent. In a social experiment, teacher leaves room, answers are available, rando we've never met encouraging us to cheat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Illusion of Asymmetric Insights</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Belief that we know others better than they know us and that we may have insights about them that they lack (but not vice versa). As explained by the fill in the blanks word game, the words don't define me, yet they do define others. CIA Officers. Judges. </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Intertemporal choice</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Refers to decisions that involve trade-offs between costs and benefits occurring at different points in time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Motivated reasoning</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cognitive phenomenon where people process information in a biased way to support their existing beliefs, desires, or emotions. Instead of evaluating evidence objectively, individuals interpret information in a way that aligns with their preferred conclusions or outcomes. Directional reasoning: When people want to arrive at a specific conclusion, they give more weight to evidence that supports their desired belief and discount or dismiss evidence that contradicts it. Accuracy reasoning: In contrast, this occurs when individuals are genuinely motivated to arrive at a correct or objective conclusion. They carefully analyze all available evidence regardless of whether it supports their initial belief. 
+Type of cognitive bias where people process information in a way that aligns with their preexisting beliefs, desires, or emotions, rather than objectively evaluating the facts</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Naive realism</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Naïve realism is a concept from social psychology and philosophy that describes the human tendency to believe that we see the world objectively, and that other people who disagree must be uninformed, irrational, or biased.  
+Naïve realism explains why disagreements can become hostile. We assume others are irrational or malicious instead of recognizing legitimate differences in perspective or interpretation. It makes it harder to understand or appreciate others’ viewpoints, since we believe our view is the only valid one.It contributes to us-vs-them mentalities in politics and culture. Each side thinks it's simply seeing "facts," while the other is deluded.In workplaces or teams, naïve realism can block constructive dialogue and creative problem-solving by dismissing dissenting ideas too quickly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ostrich Effect</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>cognitive bias where people avoid information they perceive as potentially unpleasant or negative—like an ostrich metaphorically "burying its head in the sand" to avoid danger (even though real ostriches don't actually do this).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
 Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
@@ -507,444 +818,680 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Approach which combines L1 and L2 Regularization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the absolute values of the coefficients as a penalty term. This leads to sparse models, as some coefficients become exactly zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the squared values of the coefficients as a penalty term. This increases the cost of larger parameters, encouraging the model to distribute parameters waiting This shrinks the coefficients but does not eliminate them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Exploratory Data Analysis</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Baseline represents the typical or expected behavior of an entity over a meaningful historical period. It answers the question “What is normal for this entity?” and provides context against which current state and changes can be interpreted. Baseline is conceptually stable even when its numeric value evolves, allowing models to distinguish structural differences between entities from temporary deviations. In modeling, Baseline is often foundational for defining identity and long-term segmentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Dimension</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>A Dimension is a conceptual axis of behavior or meaning that you believe exists in the real world and want your model to represent. It answers a behavioral or semantic question, not a technical one. Dimensions are stable over time, even as data sources, features, or models change (for example, we always need to understand Current State, and rate of change, even though both of what is being studied may change drastically). They are the why behind your features.
+Ultimately, it is the question, What Behaviour Matters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>An Implementation is a specific measurable representation of a dimension, derived from available data. It answers the question: “How is this dimension measured in practice?” Implementations operationalize a dimension through a defined calculation, methodology, or analytical approach. While implementations may evolve as data quality, availability, or methodology improves, they should always map clearly back to a single dimension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Momentum represents the direction and rate of change in behavior over time. It answers the question “Is this entity increasing, decreasing, or remaining stable?” and captures transitional dynamics that are not visible from state or baseline alone. Momentum is critical for detecting emerging trends, shifts in behavior, and potential future movement between segments. In modeling, Momentum often explains why change is occurring rather than what the current condition is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>A Parameter is a tuning choice that controls how an implementation is calculated, without changing what it represents. Parameters affect sensitivity, smoothness, or scale, but not conceptual meaning. They are the knobs you turn during experimentation. Examples include Window length: 3M vs 6M vs 12M, Weighting scheme: equal vs exponential, Aggregation: mean vs median
+Ultimately it is the questions, How do we compute it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>General Definition</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Volatility</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Volatility represents the consistency or variability of behavior over time. It answers the question “How stable or predictable is this entity’s behavior?” and distinguishes steady patterns from irregular or erratic ones. Volatility provides important diagnostic context, helping differentiate sustained change from noise or one-off events. In modeling, Volatility is typically explanatory or risk-related rather than defining core identity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Specific</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Measurable</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Achievable</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Relevant</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Time Bound</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Hyperparameter Tuning</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Specific</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Measurable</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Achievable</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Relevant</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Time Bound</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
 Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
@@ -952,457 +1499,599 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Exploratory Data Analysis</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Hyperparameter Tuning</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Test Relative to Baseline</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Model Evaluation</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Monitoring</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>To Be Defined</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Define Baseline</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+      <c r="D64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">	Model Summarization / Model Interpretability</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Test Relative to Baseline</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Model Summarization / Model Interpretability</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Define Baseline</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Organization - Definition</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Organization - Definition</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>List used to manage the default order of items as stored in the Notes Sheet. Specifically, there is a heirarchical order created and expected to prioritize how items are stored and filter, this list maintains that order and can be used as guidance to understand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>List used to manage the default order of items as stored in the Notes Sheet. Specifically, there is a heirarchical order created and expected to prioritize how items are stored and filter, this list maintains that order and can be used as guidance to understand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Data Engineering</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Approach which combines L1 and L2 Regularization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Data Engineering</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the absolute values of the coefficients as a penalty term. This leads to sparse models, as some coefficients become exactly zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Data Engineering</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the squared values of the coefficients as a penalty term. This increases the cost of larger parameters, encouraging the model to distribute parameters waiting This shrinks the coefficients but does not eliminate them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Validation/ Model Selection</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Validation/ Model Selection</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
         <is>
           <t>The process of choosing the most appropriate algorithm or model type for a given problem and dataset. This decision is based on factors such as data size, feature structure, interpretability needs, computational constraints, and performance requirements. Multiple candidate models are often tested and compared using consistent evaluation methods. The objective is to identify the model that provides the best balance between accuracy, stability, and practical usability.
 Similar to the process of engagement and audit followed in Feature Selection, it is critically important that actions are documented, defensible and clearly and consistently articulated to stakeholders in a meaningful manner.</t>

--- a/Streamlit/Data/consolidated_dataset.xlsx
+++ b/Streamlit/Data/consolidated_dataset.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,65 +752,157 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
+          <t>Behavioural Economics</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>What Meaning Does a KPI actually have?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+          <t>Before we figure out whether nurses have had a pay raise, first find out what is meant by “nurse.” 
+Before lamenting the prevalence of self-harm in young people, stop to consider whether you know what “self-harm” is supposed to mean. Before concluding that inequality has soared, ask, “Inequality of what?” Demanding a short, sharp answer to the question “Has inequality risen?” is not only unfair, but strangely incurious. If we are curious instead, and ask the right questions, deeper insight is within easy reach.
+Net Wealth not indicative of poverty, Doctor who just finished med school with $100k in debt.
+The billion poorest people who have a net worth of Zero might be poorer than someone with $5 as $0 doesn't add up fast.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Organizations</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Great at solving Problems. Bad at diagnosing problems. 
+You should never trust large organizations, on the best day they’re incompetent, on a bad day they’re crooked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Think about the Medium</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Weekly, daily, hourly—the metronome of the news clock changes the very nature of what is news. Daily news always seems more informative than rolling news; weekly news is typically more informative than daily news.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Unintended Consequences KPIs</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Must consider what adverse effects one might create when measuring. Doctors won't operate on sick patients. Data needs to be understood. Maximum day wait for appointment, doctors stopped taking appointments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
 Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
@@ -818,399 +910,315 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Data Preparation</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Regularization</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Preparation</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Regularization</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ElasticNet</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Approach which combines L1 and L2 Regularization.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Data Preparation</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Regularization</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Lasso</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the absolute values of the coefficients as a penalty term. This leads to sparse models, as some coefficients become exactly zero</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Data Preparation</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Regularization</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the squared values of the coefficients as a penalty term. This increases the cost of larger parameters, encouraging the model to distribute parameters waiting This shrinks the coefficients but does not eliminate them.</t>
-        </is>
-      </c>
-    </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Data Preparation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Regularization</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
+          <t>Explain what this means from a practical application of what needs to be done for the proces.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Approach which combines L1 and L2 Regularization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the absolute values of the coefficients as a penalty term. This leads to sparse models, as some coefficients become exactly zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the squared values of the coefficients as a penalty term. This increases the cost of larger parameters, encouraging the model to distribute parameters waiting This shrinks the coefficients but does not eliminate them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Exploratory Data Analysis</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Baseline represents the typical or expected behavior of an entity over a meaningful historical period. It answers the question “What is normal for this entity?” and provides context against which current state and changes can be interpreted. Baseline is conceptually stable even when its numeric value evolves, allowing models to distinguish structural differences between entities from temporary deviations. In modeling, Baseline is often foundational for defining identity and long-term segmentation.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>Dimension</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>A Dimension is a conceptual axis of behavior or meaning that you believe exists in the real world and want your model to represent. It answers a behavioral or semantic question, not a technical one. Dimensions are stable over time, even as data sources, features, or models change (for example, we always need to understand Current State, and rate of change, even though both of what is being studied may change drastically). They are the why behind your features.
 Ultimately, it is the question, What Behaviour Matters.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>Implementation</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>An Implementation is a specific measurable representation of a dimension, derived from available data. It answers the question: “How is this dimension measured in practice?” Implementations operationalize a dimension through a defined calculation, methodology, or analytical approach. While implementations may evolve as data quality, availability, or methodology improves, they should always map clearly back to a single dimension.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Momentum</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Momentum represents the direction and rate of change in behavior over time. It answers the question “Is this entity increasing, decreasing, or remaining stable?” and captures transitional dynamics that are not visible from state or baseline alone. Momentum is critical for detecting emerging trends, shifts in behavior, and potential future movement between segments. In modeling, Momentum often explains why change is occurring rather than what the current condition is.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>A Parameter is a tuning choice that controls how an implementation is calculated, without changing what it represents. Parameters affect sensitivity, smoothness, or scale, but not conceptual meaning. They are the knobs you turn during experimentation. Examples include Window length: 3M vs 6M vs 12M, Weighting scheme: equal vs exponential, Aggregation: mean vs median
 Ultimately it is the questions, How do we compute it.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>General Definition</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Volatility</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Volatility represents the consistency or variability of behavior over time. It answers the question “How stable or predictable is this entity’s behavior?” and distinguishes steady patterns from irregular or erratic ones. Volatility provides important diagnostic context, helping differentiate sustained change from noise or one-off events. In modeling, Volatility is typically explanatory or risk-related rather than defining core identity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Goal Setting</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Goal Setting</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Specific</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Goal Setting</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Requirement</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Measurable</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>General Definition</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Achievable</t>
+          <t>Volatility</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
+          <t>Volatility represents the consistency or variability of behavior over time. It answers the question “How stable or predictable is this entity’s behavior?” and distinguishes steady patterns from irregular or erratic ones. Volatility provides important diagnostic context, helping differentiate sustained change from noise or one-off events. In modeling, Volatility is typically explanatory or risk-related rather than defining core identity.</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1230,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Relevant</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
+          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
     </row>
@@ -1249,122 +1257,122 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Time Bound</t>
+          <t>Specific</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
+          <t>Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Hyperparameter Tuning</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Measurable</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
+          <t>Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Achievable</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
+          <t>Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Specific</t>
+          <t>Relevant</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
+          <t>Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Measurable</t>
+          <t>Time Bound</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
+          <t>Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Machine Learning Lifecycle</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Goal Setting</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Achievable</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
+          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
     </row>
@@ -1376,17 +1384,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Relevant</t>
-        </is>
-      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
+          <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1411,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Time Bound</t>
+          <t>Specific</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
+          <t>Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
         </is>
       </c>
     </row>
@@ -1420,17 +1428,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Goal Setting</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Measurable</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+          <t>Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
         </is>
       </c>
     </row>
@@ -1442,56 +1450,126 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>Goal Setting</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Achievable</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Goal Setting</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Relevant</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Goal Setting</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Time Bound</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
         <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Regularization</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Data Preparation</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
 Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
@@ -1499,158 +1577,96 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Explain what this means from a practical application of what needs to be done for the proces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Exploratory Data Analysis</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>Process Step</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Hyperparameter Tuning</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Test Relative to Baseline</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
-        </is>
-      </c>
-    </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
@@ -1664,12 +1680,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
+          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
     </row>
@@ -1686,12 +1702,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
+          <t>Hyperparameter Tuning</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
+          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
     </row>
@@ -1708,12 +1724,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Deployment</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
+          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
         </is>
       </c>
     </row>
@@ -1725,19 +1741,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
-        </is>
-      </c>
+          <t>Test Relative to Baseline</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1752,12 +1764,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
       </c>
     </row>
@@ -1769,17 +1781,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Model Interpretability</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>To Be Defined</t>
+          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
         </is>
       </c>
     </row>
@@ -1791,15 +1803,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Model Selection</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Define Baseline</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1814,82 +1830,86 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
+          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Model Evaluation</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Test Relative to Baseline</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>To Be Defined</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Model Interpretability</t>
+          <t>Machine Learning Lifecycle</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
-        </is>
-      </c>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Process Step</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1902,7 +1922,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1917,36 +1937,32 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Organization - Definition</t>
+          <t>Model Evaluation</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>List used to manage the default order of items as stored in the Notes Sheet. Specifically, there is a heirarchical order created and expected to prioritize how items are stored and filter, this list maintains that order and can be used as guidance to understand.</t>
-        </is>
-      </c>
+          <t>Test Relative to Baseline</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Problem Definition</t>
+          <t>Model Interpretability</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1961,80 +1977,76 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Regularization</t>
+          <t>Model Selection</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Data Engineering</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ElasticNet</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Approach which combines L1 and L2 Regularization.</t>
-        </is>
-      </c>
+          <t>Define Baseline</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Regularization</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Data Engineering</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lasso</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the absolute values of the coefficients as a penalty term. This leads to sparse models, as some coefficients become exactly zero</t>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Regularization</t>
+          <t>Organization - Definition</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Data Engineering</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the squared values of the coefficients as a penalty term. This increases the cost of larger parameters, encouraging the model to distribute parameters waiting This shrinks the coefficients but does not eliminate them.</t>
+          <t>List used to manage the default order of items as stored in the Notes Sheet. Specifically, there is a heirarchical order created and expected to prioritize how items are stored and filter, this list maintains that order and can be used as guidance to understand.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Problem Definition</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2049,49 +2061,137 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Regularization</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Data Engineering</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>ElasticNet</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
+          <t>Approach which combines L1 and L2 Regularization.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Data Engineering</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the absolute values of the coefficients as a penalty term. This leads to sparse models, as some coefficients become exactly zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Data Engineering</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the squared values of the coefficients as a penalty term. This increases the cost of larger parameters, encouraging the model to distribute parameters waiting This shrinks the coefficients but does not eliminate them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>Validation/ Model Selection</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
         <is>
           <t>The process of choosing the most appropriate algorithm or model type for a given problem and dataset. This decision is based on factors such as data size, feature structure, interpretability needs, computational constraints, and performance requirements. Multiple candidate models are often tested and compared using consistent evaluation methods. The objective is to identify the model that provides the best balance between accuracy, stability, and practical usability.
 Similar to the process of engagement and audit followed in Feature Selection, it is critically important that actions are documented, defensible and clearly and consistently articulated to stakeholders in a meaningful manner.</t>

--- a/Streamlit/Data/consolidated_dataset.xlsx
+++ b/Streamlit/Data/consolidated_dataset.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -844,65 +844,885 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bias, Fairness, and Ethics</t>
+          <t>Behavioural Economics</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Facts Vs Statistics</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+          <t>More likely to die in accident in evening than in morning. More drivers in evening than in morning.
+More likely to die in clear weather than fog. More time occurs without fog, what does it actually mean???
+9:1000 vs 16:1000 deaths in Navy vs NY. Who is in Navy, young healthy men, vs everyone else.
+Polio record cases 1952, more babies, financial incentives, changes on reporting standards, etc..
+Population in rural China, 28M than 5 years later 108M. Survey 1 was related to Military conscription, Survey 2 famine and relief</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fact Believability</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Facts about this epidemic that have lasted a few days are far more reliable than the latest ‘facts’ that have just come out, which may be erroneous or unrepresentative and thus misleading . . . a question that today can be answered [by] only informed belief may perhaps be answered with a fact tomorrow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Review Demographics</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Evaluate model performance across key demographic or operational groups. Identifies potential unfair or unequal outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Test unitended discrimination</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Review sensitive features and proxy variables. Prevents unintended discrimination.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Document Fairness Checks</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Document fairness checks and mitigation steps. Supports transparency, accountability, and compliance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Deliver Simplicity</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Do not make the user think</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Do Not Demand Recall</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Do not make the user remember. If the Speaker utters 120 word a minute, the audience is thinking 500.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Visuals in 2D</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Do not use 3D unless absolutely necessary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Avoid Pie Charts</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pie Charts. They Suck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Do Not Offend Your Audience</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Do Not Let Predjudices Close Your Mind</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Don’t waste the advantage that thought has over speech</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Hearing vs Listening</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Most were born hearing well, EVERYONE must learn to listen well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Always Thank Your Audience</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Choosing a Medium</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>While not always give a choice, it is important to be mindful that the ability to communicate, in terms of breadth, depth, clarity and pursuaiveness differ across mediums, so one must be plan and execute accordingly. Additional there might be a preference/ opportunity to advocate for a distinct and preferred medium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Understand Your Audience</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Understand Your Strategy</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Beyond understanding Your Message, you need to think about how you are going to articulate your story, your goals, motivation, priority. Reconizing differences between things that have great personal meaning, business relevance, or simply mandated work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Choosing a Medium</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>While not always give a choice, it is important to be mindful that the ability to communicate, in terms of breadth, depth, clarity and pursuaiveness differ across mediums, so one must be plan and execute accordingly. Additional there might be a preference/ opportunity to advocate for a distinct and preferred medium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Understand Your Visuals</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Message Spareness</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Utilize a less is more approach, whether that is Slides, Words, Pages, Etc. Less is more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Re-enforce the Message</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Deliver Simplicity</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Do not make the user think</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Do Not Demand Recall</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Do not make the user remember. If the Speaker utters 120 word a minute, the audience is thinking 500.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Visuals in 2D</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Do not use 3D unless absolutely necessary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Avoid Pie Charts</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pie Charts. They Suck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Do Not Offend Your Audience</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Do Not Let Predjudices Close Your Mind</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Don’t waste the advantage that thought has over speech</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Hearing vs Listening</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Most were born hearing well, EVERYONE must learn to listen well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Always Thank Your Audience</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>General Expectations</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Measuing Effectiveness</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>How can one measure how effective/ineffective a particular communication was?</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Data Collection</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Label Data</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Ensure that All data is defined, and classified. Including Semantic and Functional Definitions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Data Collection</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ensure Sufficient Data Exists</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Ensure that model has sufficient representation (Covered from at a Minimum Semantic and Functional Perspective).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Data Collection</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Challenges from Missing Data</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What concessions have we made due to a lack of data availability, and how are those going to undermine the work we plan on doing. </t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Data Collection</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Who Owns the Data</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Who is the Data Steward, and Process owners? Are they and have they been involved. Operationally do we have integrity, consistency and availability to include?</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
 Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
@@ -910,666 +1730,1462 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
         <is>
           <t>Regularization</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Explain what this means from a practical application of what needs to be done for the proces.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Regularization</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>ElasticNet</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Approach which combines L1 and L2 Regularization.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>Regularization</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the absolute values of the coefficients as a penalty term. This leads to sparse models, as some coefficients become exactly zero</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Regularization</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the squared values of the coefficients as a penalty term. This increases the cost of larger parameters, encouraging the model to distribute parameters waiting This shrinks the coefficients but does not eliminate them.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Package Model for Deployment with everything necessary</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Package the model with all required preprocessing steps. Ensures predictions in production match training conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Test in different environments</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Test the model in a staging or test environment. Utilize Dedicated Environment. Reduces risk of failures in production.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Version Control</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Create a versioned and reproducible deployment artifact. Supports rollback, auditing, and maintenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Exploratory Data Analysis</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ratios or Observed Values</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>What ratios or proportions could better represent behavior than raw values? Many real-world patterns depend on relative size (e.g., debt-to-income, usage-to-capacity), so ratios often reveal signal that absolute values hide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Include Interactions</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>What combinations or interactions might reflect how factors work together? Some outcomes are driven by the interaction between variables (e.g., high balance and high transaction frequency), so combining features can expose relationships a model might miss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>How does Time Impact?</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>What time-based changes or aggregates could capture trends or stability? Differences, growth rates, or rolling averages often reflect momentum or consistency, which are strong predictors of future behavior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Explain Feature Practical Relevance</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Generate feature importance or explanation outputs. Helps understand what drives model predictions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Remove Unnecessary Features</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Remove features with high missingness or low variance. Reduces noise and improves model stability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Understand Feature Correlations</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Check for multicollinearity or redundant features. Helps prevent unstable models and improves interpretability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Document Feature Statistical Relevance</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Validate selected features using model or statistical methods. Ensures the retained features actually contribute to predictive performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Avoid Ambguity</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Avoid ambiguous features. Is a Banana ripe, who says so?</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Is a feature Random?</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Careful when something is truly random generated, Atmospheric Change, Earthquakes, Stocks. Very difficult, if not impossible to predict.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Model Robustness</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>How robust is your model to change and what is it actually predicting.  MNIST performance when tilting Images, of adding noise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Test Individual Feature Importance</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Need to understand how much an individual feature contributes beyond what the other features already provide. A feature has incremental value and removing or disrupting it should decrease performance. This supports inclusion of value add feature, opposed to those which create redundancy or noise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Reconstruction Error in Autoencoders</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Does this feature improve the model’s ability to represent and reconstruct the data? An autoencoder learns to compress the input data into a smaller latent representation and then reconstruct the original data. Reconstruction error measures the difference between the original observations and the reconstructed output; lower error generally means the model has preserved more of the data’s structure.
+For feature selection, you can remove, mask, or add one feature at a time and observe how reconstruction error changes. A substantial increase in error after removing a feature suggests that the feature contains important information, although highly correlated features may appear less important because another feature can reconstruct the same information.
+For model selection, reconstruction error can help compare autoencoder architectures, latent-space sizes, regularization settings, or feature subsets. However, the lowest reconstruction error is not always the best choice because an overly complex model may simply memorize the training data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Mutual Information with Latent Cluster Assignment</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>How strongly is this feature associated with the cluster structure the model discovered? Mutual information measures how much knowing one variable reduces uncertainty about another. In this context, it measures the association between a feature and the cluster labels produced by an unsupervised model.
+For feature selection, features with high mutual information are strongly associated with the discovered cluster structure and may be useful for distinguishing groups. Features with very low mutual information may contribute little to the final segmentation, although they could still affect the clustering indirectly through interactions with other features.
+For model selection, mutual information can help compare clustering solutions by examining whether their assignments are meaningfully related to the input features. It can also be used to compare cluster solutions across model runs, although metrics such as adjusted mutual information are usually more appropriate when directly comparing two sets of cluster labels. Because the cluster assignments come from the same data, this does not independently prove that the clusters are valid. It explains the model’s segmentation rather than confirming that the segmentation represents a real-world truth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Permutation for Clustering</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Permutation importance measures the value of a feature by randomly shuffling its values while leaving the other features unchanged. Shuffling breaks the feature’s relationship with the observations; if cluster quality, assignment consistency, or model performance worsens, the feature was contributing useful information.
+For feature selection, features that cause a large decline in clustering performance when shuffled are considered important. Features whose permutation has little effect may be redundant, irrelevant, or dominated by stronger features and could be candidates for removal.
+For model selection, permutation can help compare how dependent different clustering models are on particular features. A model whose results are driven by one unstable feature may be less desirable than a model that uses several meaningful features and remains stable under small perturbations.
+Possible measures after permutation include: Change in silhouette score, Increase in inertia, Change in Davies–Bouldin or Calinski–Harabasz scores, Percentage of observations assigned to a different cluster, Reduction in cluster stability across repeated runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>Baseline represents the typical or expected behavior of an entity over a meaningful historical period. It answers the question “What is normal for this entity?” and provides context against which current state and changes can be interpreted. Baseline is conceptually stable even when its numeric value evolves, allowing models to distinguish structural differences between entities from temporary deviations. In modeling, Baseline is often foundational for defining identity and long-term segmentation.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Dimension</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>A Dimension is a conceptual axis of behavior or meaning that you believe exists in the real world and want your model to represent. It answers a behavioral or semantic question, not a technical one. Dimensions are stable over time, even as data sources, features, or models change (for example, we always need to understand Current State, and rate of change, even though both of what is being studied may change drastically). They are the why behind your features.
 Ultimately, it is the question, What Behaviour Matters.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Implementation</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>An Implementation is a specific measurable representation of a dimension, derived from available data. It answers the question: “How is this dimension measured in practice?” Implementations operationalize a dimension through a defined calculation, methodology, or analytical approach. While implementations may evolve as data quality, availability, or methodology improves, they should always map clearly back to a single dimension.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Momentum</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>Momentum represents the direction and rate of change in behavior over time. It answers the question “Is this entity increasing, decreasing, or remaining stable?” and captures transitional dynamics that are not visible from state or baseline alone. Momentum is critical for detecting emerging trends, shifts in behavior, and potential future movement between segments. In modeling, Momentum often explains why change is occurring rather than what the current condition is.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>A Parameter is a tuning choice that controls how an implementation is calculated, without changing what it represents. Parameters affect sensitivity, smoothness, or scale, but not conceptual meaning. They are the knobs you turn during experimentation. Examples include Window length: 3M vs 6M vs 12M, Weighting scheme: equal vs exponential, Aggregation: mean vs median
 Ultimately it is the questions, How do we compute it.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Volatility</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>Volatility represents the consistency or variability of behavior over time. It answers the question “How stable or predictable is this entity’s behavior?” and distinguishes steady patterns from irregular or erratic ones. Volatility provides important diagnostic context, helping differentiate sustained change from noise or one-off events. In modeling, Volatility is typically explanatory or risk-related rather than defining core identity.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>General Expectations</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Specific</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Measurable</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Achievable</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Relevant</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Time Bound</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>Hyperparameter Tuning</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Hyperparameter Tuning</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Define Search Space</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Define a clear search space for key hyperparameters. Ensures tuning focuses on meaningful configurations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Hyperparameter Tuning</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Cross Validation to Prevent Overfitting</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Use cross-validation or a validation set for tuning. Prevents overfitting to the training data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Hyperparameter Tuning</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Document Results</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Record best parameters and associated performance. Allows reproducibility and comparison across experiments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Hyperparameter Tuning</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Explicit Exploration. Avoid needless and endless tuning</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Define Parameters you will tune and approach to tuning before you commence tuning. Do not simply tune model to optimal parameters without considering what you are actually doing, and its ability to generalize.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>To Be Defined</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>Specific</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>Measurable</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>Achievable</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>Relevant</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>Time Bound</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Desired State Metrics</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Current State Analysis</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Root Cause Assessment</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Historical Overview</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Baseline Metrics (Current State)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Understand KPIs which are meaningful.</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Attempt to explicitly define outcomes and relevant KPIs for those outcomes. Where that can not happen, it is important to understand why that can not happen. What is happening if we don't have and follow metrics. IE. The Account Opening Process is not efficient and needs to improve, The Internet Banking Experience is poor, and does not attract customers. How do you monitor this, how can you define this, how can you prove this,  how do you expect this to change and measure that change.
+How will the project and efforts be measured where success can not be objectively measured? How will resources be allocated when it remains unclear what benefit or risk exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>What Lens is Problem Defined?</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Must be careful at how problem is defined. Is it defined in the context of the already identified solution, has it been validated and is the problem distinct from the analysis and potential solution, or have we leaked into the process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Stakeholder Investment?</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>How Invested are stakeholders in defining the problem? What is their view of the process/ project, how invested, interested and engaged are they. What are their personal goals and motivation, speed, accuracy, validation of ideology?</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Really Understand Problem Statement</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk and the likelihood of not meeting expectations, frustration, or material change to purpose, scope or priority is inevitable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
         <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Data Collection</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Label Data</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Ensure that All data is defined, and classified. Including Semantic and Functional Definitions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Data Collection</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ensure Sufficient Data Exists</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Ensure that model has sufficient representation (Covered from at a Minimum Semantic and Functional Perspective).</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Data Collection</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Challenges from Missing Data</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What concessions have we made due to a lack of data availability, and how are those going to undermine the work we plan on doing. </t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Data Collection</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Who Owns the Data</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Who is the Data Steward, and Process owners? Are they and have they been involved. Operationally do we have integrity, consistency and availability to include?</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
 Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
@@ -1577,624 +3193,2915 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Regularization</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>Explain what this means from a practical application of what needs to be done for the proces.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Approach which combines L1 and L2 Regularization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the absolute values of the coefficients as a penalty term. This leads to sparse models, as some coefficients become exactly zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the squared values of the coefficients as a penalty term. This increases the cost of larger parameters, encouraging the model to distribute parameters waiting This shrinks the coefficients but does not eliminate them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
         <is>
           <t>Exploratory Data Analysis</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Ratios or Observed Values</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>What ratios or proportions could better represent behavior than raw values? Many real-world patterns depend on relative size (e.g., debt-to-income, usage-to-capacity), so ratios often reveal signal that absolute values hide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Include Interactions</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>What combinations or interactions might reflect how factors work together? Some outcomes are driven by the interaction between variables (e.g., high balance and high transaction frequency), so combining features can expose relationships a model might miss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Feature Engineering</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>How does Time Impact?</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>What time-based changes or aggregates could capture trends or stability? Differences, growth rates, or rolling averages often reflect momentum or consistency, which are strong predictors of future behavior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Hyperparameter Tuning</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Test Relative to Baseline</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Model Interpretability</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Deployment</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Bias, Fairness, and Ethics</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>To Be Defined</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Explain Feature Practical Relevance</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Generate feature importance or explanation outputs. Helps understand what drives model predictions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Remove Unnecessary Features</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Remove features with high missingness or low variance. Reduces noise and improves model stability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Understand Feature Correlations</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Check for multicollinearity or redundant features. Helps prevent unstable models and improves interpretability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Document Feature Statistical Relevance</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Validate selected features using model or statistical methods. Ensures the retained features actually contribute to predictive performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Avoid Ambguity</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Avoid ambiguous features. Is a Banana ripe, who says so?</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Is a feature Random?</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Careful when something is truly random generated, Atmospheric Change, Earthquakes, Stocks. Very difficult, if not impossible to predict.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Model Robustness</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>How robust is your model to change and what is it actually predicting.  MNIST performance when tilting Images, of adding noise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Test Individual Feature Importance</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Need to understand how much an individual feature contributes beyond what the other features already provide. A feature has incremental value and removing or disrupting it should decrease performance. This supports inclusion of value add feature, opposed to those which create redundancy or noise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Reconstruction Error in Autoencoders</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Does this feature improve the model’s ability to represent and reconstruct the data? An autoencoder learns to compress the input data into a smaller latent representation and then reconstruct the original data. Reconstruction error measures the difference between the original observations and the reconstructed output; lower error generally means the model has preserved more of the data’s structure.
+For feature selection, you can remove, mask, or add one feature at a time and observe how reconstruction error changes. A substantial increase in error after removing a feature suggests that the feature contains important information, although highly correlated features may appear less important because another feature can reconstruct the same information.
+For model selection, reconstruction error can help compare autoencoder architectures, latent-space sizes, regularization settings, or feature subsets. However, the lowest reconstruction error is not always the best choice because an overly complex model may simply memorize the training data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Mutual Information with Latent Cluster Assignment</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>How strongly is this feature associated with the cluster structure the model discovered? Mutual information measures how much knowing one variable reduces uncertainty about another. In this context, it measures the association between a feature and the cluster labels produced by an unsupervised model.
+For feature selection, features with high mutual information are strongly associated with the discovered cluster structure and may be useful for distinguishing groups. Features with very low mutual information may contribute little to the final segmentation, although they could still affect the clustering indirectly through interactions with other features.
+For model selection, mutual information can help compare clustering solutions by examining whether their assignments are meaningfully related to the input features. It can also be used to compare cluster solutions across model runs, although metrics such as adjusted mutual information are usually more appropriate when directly comparing two sets of cluster labels. Because the cluster assignments come from the same data, this does not independently prove that the clusters are valid. It explains the model’s segmentation rather than confirming that the segmentation represents a real-world truth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Feature Selection</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Permutation for Clustering</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Permutation importance measures the value of a feature by randomly shuffling its values while leaving the other features unchanged. Shuffling breaks the feature’s relationship with the observations; if cluster quality, assignment consistency, or model performance worsens, the feature was contributing useful information.
+For feature selection, features that cause a large decline in clustering performance when shuffled are considered important. Features whose permutation has little effect may be redundant, irrelevant, or dominated by stronger features and could be candidates for removal.
+For model selection, permutation can help compare how dependent different clustering models are on particular features. A model whose results are driven by one unstable feature may be less desirable than a model that uses several meaningful features and remains stable under small perturbations.
+Possible measures after permutation include: Change in silhouette score, Increase in inertia, Change in Davies–Bouldin or Calinski–Harabasz scores, Percentage of observations assigned to a different cluster, Reduction in cluster stability across repeated runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Define Baseline</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Model Evaluation</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Test Relative to Baseline</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Model Interpretability</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Model Selection</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Define Baseline</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Organization - Definition</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>List used to manage the default order of items as stored in the Notes Sheet. Specifically, there is a heirarchical order created and expected to prioritize how items are stored and filter, this list maintains that order and can be used as guidance to understand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Problem Definition</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Regularization</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Data Engineering</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>ElasticNet</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Approach which combines L1 and L2 Regularization.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Regularization</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Data Engineering</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Lasso</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the absolute values of the coefficients as a penalty term. This leads to sparse models, as some coefficients become exactly zero</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Regularization</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Data Engineering</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the squared values of the coefficients as a penalty term. This increases the cost of larger parameters, encouraging the model to distribute parameters waiting This shrinks the coefficients but does not eliminate them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Validation/ Model Selection</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>The process of choosing the most appropriate algorithm or model type for a given problem and dataset. This decision is based on factors such as data size, feature structure, interpretability needs, computational constraints, and performance requirements. Multiple candidate models are often tested and compared using consistent evaluation methods. The objective is to identify the model that provides the best balance between accuracy, stability, and practical usability.
 Similar to the process of engagement and audit followed in Feature Selection, it is critically important that actions are documented, defensible and clearly and consistently articulated to stakeholders in a meaningful manner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Define Baseline</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Document Results and Choice</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Ensure that final selection is documented and agreed by appropriate stakeholders, who have been part of entire development journey, understand and are aware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Define Validation Approach in Advance</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Use cross-validation or a structured validation approach. Provides a more reliable estimate of model performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Validate no Leakage</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Ensure no data leakage between training and validation sets. Prevents overly optimistic performance estimates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Validate consistency over time</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Confirm performance stability across folds or time splits. Indicates the model is robust and generalizable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>How will Model Learn?</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Must select an appropriate learning method. Supervised, Unsupervised, Semi-Supervised, Reinforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>What Problem is the Model Solving?</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Must select an appropriate method. Classification, Regression, Clustering, Dimensionality Reduction, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>What Model/Algo is being used to solve the problem</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Document founational assessment at the outset, can revisit during Model Selection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Select Model(s) based on Objective</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Define what the objective of the model work is, state what is being measured and why. 
+Document all models which will be considered, including why they are appropriate and where models are excluded, insure rationale available. Compare multiple model types using the same validation approach. Ensures a fair comparison and better-informed model choice.
+Important to define what type of model is being used, what type of </t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Create and Understand Baseline</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Create Simplified Baseline Model, use this are reference. Ensure that this is communicated to Stakeholders, so they understand both the benchmark and expectation, to determine relevance. Should align with Goals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Performance vs Cost vs Practicality</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Consider interpretability, performance, and computational cost. Balances practical constraints with predictive accuracy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>How Many Examples are Needed?</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Distinct for every type of Method or approach. Need to be comfortable that the dataset has enough examples and that they represent a population to which you believe is representive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Understand what your model is actually solving and how.</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Models will cheat and can solve problems which appear to be optimal, but they might not be solving what you expect or require, they might be finding patterns in the data which you do not see. An Example of this would a classification model with Wolves and Dogs,  many wolf photos happened to be taken in snowy environments, while dog photos were often taken indoors or on grass. The model learned to detect snow, not animals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Speed vs Accuracy</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>The most accurate model is not always the most valuable. Delivering a good solution quickly often creates more business value than spending significant time chasing small improvements in performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Accuracy vs Repeatability</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>A highly accurate result has limited value if it cannot be reproduced consistently. Prioritize workflows, data pipelines, and model training processes that generate reliable and repeatable outcomes over one-time exceptional results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Correlation vs Causation</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Machine learning identifies relationships in data but does not prove why those relationships exist. Treat model outputs as evidence of association and rely on experimentation or domain expertise to establish causal conclusions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Stability over Uniqueness</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Prefer models that perform consistently across different datasets and over time rather than those that achieve exceptional results only under specific conditions. Reliable, generalizable models are more valuable than highly specialized ones that are difficult to maintain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Interpretability over Novelty</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>A simple model that stakeholders understand and trust is often more useful than a complex state-of-the-art model with marginal performance gains. Choose complexity only when it delivers meaningful improvements that justify reduced transparency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Repeatability over Perfection</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Machine learning is an iterative process, not a search for a flawless model. Build solutions that others can rerun, validate, and improve, knowing that incremental refinement typically delivers more long-term value than pursuing perfection from the outset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Train, Test, Validation Split</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Is split between Training, Testing and Validation appropriate, fair and responsible. Validate and document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Convergence Achieved?</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Verify model converges and loss decreases during training. Confirms the model is learning meaningful patterns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Logging of Parameters</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Log model parameters, features, training configuration and results. Supports reproducibility and troubleshooting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Any dataset can be optimized</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Any data set can be optimized, even when there is NO relation it will generalize. Remember the goal, ability to generalize, not simply predict training.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Hyperparameter Tuning</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Hyperparameter Tuning</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Define Search Space</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Define a clear search space for key hyperparameters. Ensures tuning focuses on meaningful configurations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Hyperparameter Tuning</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Cross Validation to Prevent Overfitting</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Use cross-validation or a validation set for tuning. Prevents overfitting to the training data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Hyperparameter Tuning</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Document Results</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Record best parameters and associated performance. Allows reproducibility and comparison across experiments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Hyperparameter Tuning</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Explicit Exploration. Avoid needless and endless tuning</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Define Parameters you will tune and approach to tuning before you commence tuning. Do not simply tune model to optimal parameters without considering what you are actually doing, and its ability to generalize.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Test Relative to Baseline</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Use Relevant Metrics</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Use metrics appropriate to the problem type and business goal. Ensures the model is evaluated in a way that reflects real-world impact.
+This should change to be more specific. Define Thresholds. Test Thresholds, recommend based on X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Keep Hold Out</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Evaluate performance on a hold-out test set. Provides an unbiased estimate of generalization performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Review Overfitting</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Check for overfitting by comparing training and test results. Identifies models that may not perform well in production.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Explain Selected Features using Words</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Utilize feature importance metrics to visualize and explain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Results/Outcome should not be shocking</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This should be a formal step as engagement along the way is predicated on this as a core tenet and principle. If people seem shocked, embed stronger components earlier in process. </t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Document Beyond Communciation</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Document model behavior and major drivers. Supports stakeholder understanding and auditability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Package Model for Deployment with everything necessary</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Package the model with all required preprocessing steps. Ensures predictions in production match training conditions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Test in different environments</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Test the model in a staging or test environment. Utilize Dedicated Environment. Reduces risk of failures in production.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Deployment</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Version Control</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Create a versioned and reproducible deployment artifact. Supports rollback, auditing, and maintenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Overtime Perforamnce Monitoring</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Track model performance metrics over time. Detects degradation or drift after deployment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Monitor Input Drift</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Monitor input data distributions for drift. Identifies changes in data that could affect predictions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Clearly define production context windows</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Define triggers for retraining or model review. Ensures timely corrective action when performance declines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Review Demographics</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Evaluate model performance across key demographic or operational groups. Identifies potential unfair or unequal outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Test unitended discrimination</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Review sensitive features and proxy variables. Prevents unintended discrimination.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Bias, Fairness, and Ethics</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Document Fairness Checks</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Document fairness checks and mitigation steps. Supports transparency, accountability, and compliance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Measuing Effectiveness</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>How can one measure how effective/ineffective a particular communication was?</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Message Spareness</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Utilize a less is more approach, whether that is Slides, Words, Pages, Etc. Less is more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Test Relative to Baseline</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Use Relevant Metrics</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Use metrics appropriate to the problem type and business goal. Ensures the model is evaluated in a way that reflects real-world impact.
+This should change to be more specific. Define Thresholds. Test Thresholds, recommend based on X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Keep Hold Out</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Evaluate performance on a hold-out test set. Provides an unbiased estimate of generalization performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Model Evaluation</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Review Overfitting</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Check for overfitting by comparing training and test results. Identifies models that may not perform well in production.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Explain Selected Features using Words</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Utilize feature importance metrics to visualize and explain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Results/Outcome should not be shocking</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This should be a formal step as engagement along the way is predicated on this as a core tenet and principle. If people seem shocked, embed stronger components earlier in process. </t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Model Interpretability</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Document Beyond Communciation</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Document model behavior and major drivers. Supports stakeholder understanding and auditability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>The process of choosing the most appropriate algorithm or model type for a given problem and dataset. This decision is based on factors such as data size, feature structure, interpretability needs, computational constraints, and performance requirements. Multiple candidate models are often tested and compared using consistent evaluation methods. The objective is to identify the model that provides the best balance between accuracy, stability, and practical usability.
+Similar to the process of engagement and audit followed in Feature Selection, it is critically important that actions are documented, defensible and clearly and consistently articulated to stakeholders in a meaningful manner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Define Baseline</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Document Results and Choice</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Ensure that final selection is documented and agreed by appropriate stakeholders, who have been part of entire development journey, understand and are aware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Define Validation Approach in Advance</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Use cross-validation or a structured validation approach. Provides a more reliable estimate of model performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Validate no Leakage</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Ensure no data leakage between training and validation sets. Prevents overly optimistic performance estimates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Validate consistency over time</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Confirm performance stability across folds or time splits. Indicates the model is robust and generalizable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>How will Model Learn?</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Must select an appropriate learning method. Supervised, Unsupervised, Semi-Supervised, Reinforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>What Problem is the Model Solving?</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Must select an appropriate method. Classification, Regression, Clustering, Dimensionality Reduction, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>What Model/Algo is being used to solve the problem</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Document founational assessment at the outset, can revisit during Model Selection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Select Model(s) based on Objective</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Define what the objective of the model work is, state what is being measured and why. 
+Document all models which will be considered, including why they are appropriate and where models are excluded, insure rationale available. Compare multiple model types using the same validation approach. Ensures a fair comparison and better-informed model choice.
+Important to define what type of model is being used, what type of </t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Create and Understand Baseline</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Create Simplified Baseline Model, use this are reference. Ensure that this is communicated to Stakeholders, so they understand both the benchmark and expectation, to determine relevance. Should align with Goals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Performance vs Cost vs Practicality</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Consider interpretability, performance, and computational cost. Balances practical constraints with predictive accuracy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>How Many Examples are Needed?</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Distinct for every type of Method or approach. Need to be comfortable that the dataset has enough examples and that they represent a population to which you believe is representive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Understand what your model is actually solving and how.</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Models will cheat and can solve problems which appear to be optimal, but they might not be solving what you expect or require, they might be finding patterns in the data which you do not see. An Example of this would a classification model with Wolves and Dogs,  many wolf photos happened to be taken in snowy environments, while dog photos were often taken indoors or on grass. The model learned to detect snow, not animals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Speed vs Accuracy</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>The most accurate model is not always the most valuable. Delivering a good solution quickly often creates more business value than spending significant time chasing small improvements in performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Accuracy vs Repeatability</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>A highly accurate result has limited value if it cannot be reproduced consistently. Prioritize workflows, data pipelines, and model training processes that generate reliable and repeatable outcomes over one-time exceptional results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Correlation vs Causation</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Machine learning identifies relationships in data but does not prove why those relationships exist. Treat model outputs as evidence of association and rely on experimentation or domain expertise to establish causal conclusions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Stability over Uniqueness</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Prefer models that perform consistently across different datasets and over time rather than those that achieve exceptional results only under specific conditions. Reliable, generalizable models are more valuable than highly specialized ones that are difficult to maintain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Interpretability over Novelty</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>A simple model that stakeholders understand and trust is often more useful than a complex state-of-the-art model with marginal performance gains. Choose complexity only when it delivers meaningful improvements that justify reduced transparency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Model Selection</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Repeatability over Perfection</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Machine learning is an iterative process, not a search for a flawless model. Build solutions that others can rerun, validate, and improve, knowing that incremental refinement typically delivers more long-term value than pursuing perfection from the outset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Overtime Perforamnce Monitoring</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Track model performance metrics over time. Detects degradation or drift after deployment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Monitor Input Drift</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Monitor input data distributions for drift. Identifies changes in data that could affect predictions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Clearly define production context windows</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Define triggers for retraining or model review. Ensures timely corrective action when performance declines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Organization - Definition</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>List used to manage the default order of items as stored in the Notes Sheet. Specifically, there is a heirarchical order created and expected to prioritize how items are stored and filter, this list maintains that order and can be used as guidance to understand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Desired State Metrics</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Current State Analysis</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Root Cause Assessment</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Historical Overview</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Baseline Metrics (Current State)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Understand KPIs which are meaningful.</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Attempt to explicitly define outcomes and relevant KPIs for those outcomes. Where that can not happen, it is important to understand why that can not happen. What is happening if we don't have and follow metrics. IE. The Account Opening Process is not efficient and needs to improve, The Internet Banking Experience is poor, and does not attract customers. How do you monitor this, how can you define this, how can you prove this,  how do you expect this to change and measure that change.
+How will the project and efforts be measured where success can not be objectively measured? How will resources be allocated when it remains unclear what benefit or risk exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>What Lens is Problem Defined?</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Must be careful at how problem is defined. Is it defined in the context of the already identified solution, has it been validated and is the problem distinct from the analysis and potential solution, or have we leaked into the process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Stakeholder Investment?</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>How Invested are stakeholders in defining the problem? What is their view of the process/ project, how invested, interested and engaged are they. What are their personal goals and motivation, speed, accuracy, validation of ideology?</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Problem Definition</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Really Understand Problem Statement</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk and the likelihood of not meeting expectations, frustration, or material change to purpose, scope or priority is inevitable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Re-enforce the Message</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Approach which combines L1 and L2 Regularization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the absolute values of the coefficients as a penalty term. This leads to sparse models, as some coefficients become exactly zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Regularization</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Data Preparation</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the squared values of the coefficients as a penalty term. This increases the cost of larger parameters, encouraging the model to distribute parameters waiting This shrinks the coefficients but does not eliminate them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Train, Test, Validation Split</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Is split between Training, Testing and Validation appropriate, fair and responsible. Validate and document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Convergence Achieved?</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Verify model converges and loss decreases during training. Confirms the model is learning meaningful patterns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Logging of Parameters</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Log model parameters, features, training configuration and results. Supports reproducibility and troubleshooting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Warning</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Any dataset can be optimized</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Any data set can be optimized, even when there is NO relation it will generalize. Remember the goal, ability to generalize, not simply predict training.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Understand Your Audience</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Understand Your Strategy</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Beyond understanding Your Message, you need to think about how you are going to articulate your story, your goals, motivation, priority. Reconizing differences between things that have great personal meaning, business relevance, or simply mandated work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Understand Your Visuals</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
       </c>
     </row>

--- a/Streamlit/Data/consolidated_dataset.xlsx
+++ b/Streamlit/Data/consolidated_dataset.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D261"/>
+  <dimension ref="A1:D341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,112 +441,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Behavioural Economics</t>
+          <t>Activation Function</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Anchoring Effect</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>A cognitive bias where people rely too heavily on the first piece of information (the “anchor”) when making decisions. Once an anchor is set, it influences subsequent judgments, even if it’s arbitrary or unrelated. For example, when asked whether the Eiffel Tower is taller or shorter than 500 feet, people’s estimates will cluster around that number. This bias can affect pricing, negotiations, and even forecasting.</t>
-        </is>
-      </c>
+          <t>Leaky Relu</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Behavioural Economics</t>
+          <t>Activation Function</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Base Rate Fallacy</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>People ignore or undervalue general statistical information (the base rate) and focus instead on specific information, often leading to incorrect conclusions. In decision-making, individuals may give more weight to anecdotal or vivid information, despite the broader statistical reality that should influence their judgment. Imagine a test for a rare disease that is 95% accurate. The disease affects 1 in 10,000 people. If a person tests positive, many might assume the likelihood of them having the disease is high. However, considering the base rate (the rarity of the disease), the probability of actually having the disease is still very low. In this scenario, the base rate fallacy would be ignoring the low prevalence of the disease (the base rate) and overestimating the accuracy of the test result, leading to an exaggerated belief in the likelihood of the person having the disease. The fallacy demonstrates how people's intuitive reasoning often neglects the significance of background statistical data in favor of more attention-grabbing or salient information.</t>
-        </is>
-      </c>
+          <t>Relu</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Behavioural Economics</t>
+          <t>Activation Function</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bureaucratic Politics</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Organization decision making paradigm in which decisions are made based solely on who is making the decision, specifically, they will decide in their own best interests. Counters prevalent theory in which a rational, fair or logical decision making process will occur.</t>
-        </is>
-      </c>
+          <t>Sigmoid</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Behavioural Economics</t>
+          <t>Activation Function</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Biased Assimilation</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tendency to interpret information in a way that supports a desired conclusion. </t>
-        </is>
-      </c>
+          <t>Softmax</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Behavioural Economics</t>
+          <t>Activation Function</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Blind spot bias</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Cognitive bias where people are unaware of their own biases, while easily recognizing the biases in others.  People tend to believe they are more objective, rational, and less susceptible to biases than others, even though they may exhibit the same biases in their own thinking. Self-awareness gap: People can easily identify cognitive biases (like confirmation bias, motivated reasoning, or stereotyping) in others, but fail to recognize these biases in themselves. Overconfidence in objectivity: Individuals often overestimate their own ability to reason without bias, which can lead to an inflated sense of confidence in their decisions and beliefs. Resistance to feedback: Blind spot bias can make people resistant to feedback, because they believe that they’re viewing situations or information more objectively than they actually are.</t>
-        </is>
-      </c>
+          <t>Tanh</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -561,126 +541,126 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Anchoring Effect</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A cognitive bias where people rely too heavily on the first piece of information (the “anchor”) when making decisions. Once an anchor is set, it influences subsequent judgments, even if it’s arbitrary or unrelated. For example, when asked whether the Eiffel Tower is taller or shorter than 500 feet, people’s estimates will cluster around that number. This bias can affect pricing, negotiations, and even forecasting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Base Rate Fallacy</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>People ignore or undervalue general statistical information (the base rate) and focus instead on specific information, often leading to incorrect conclusions. In decision-making, individuals may give more weight to anecdotal or vivid information, despite the broader statistical reality that should influence their judgment. Imagine a test for a rare disease that is 95% accurate. The disease affects 1 in 10,000 people. If a person tests positive, many might assume the likelihood of them having the disease is high. However, considering the base rate (the rarity of the disease), the probability of actually having the disease is still very low. In this scenario, the base rate fallacy would be ignoring the low prevalence of the disease (the base rate) and overestimating the accuracy of the test result, leading to an exaggerated belief in the likelihood of the person having the disease. The fallacy demonstrates how people's intuitive reasoning often neglects the significance of background statistical data in favor of more attention-grabbing or salient information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bureaucratic Politics</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Organization decision making paradigm in which decisions are made based solely on who is making the decision, specifically, they will decide in their own best interests. Counters prevalent theory in which a rational, fair or logical decision making process will occur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Biased Assimilation</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tendency to interpret information in a way that supports a desired conclusion. </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Blind spot bias</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cognitive bias where people are unaware of their own biases, while easily recognizing the biases in others.  People tend to believe they are more objective, rational, and less susceptible to biases than others, even though they may exhibit the same biases in their own thinking. Self-awareness gap: People can easily identify cognitive biases (like confirmation bias, motivated reasoning, or stereotyping) in others, but fail to recognize these biases in themselves. Overconfidence in objectivity: Individuals often overestimate their own ability to reason without bias, which can lead to an inflated sense of confidence in their decisions and beliefs. Resistance to feedback: Blind spot bias can make people resistant to feedback, because they believe that they’re viewing situations or information more objectively than they actually are.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>Confirmation Bias</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Also known as Selective Perception. What people see can be strongly shaped by what they believe, using the example of a study which occurred during a especially dirty Princeton Dartmouth Football game. After the game people were asked to comment which team was "Dirtier" and results were based on which team individuals had allegiance with.
 Tendency to search for, interpret, and remember information in a way that confirms one’s preexisting beliefs or hypotheses. People often ignore or downplay evidence that contradicts their views. This bias can reinforce stereotypes, polarize opinions, and skew data interpretation. It’s especially important to watch for in research, media consumption, and decision-making.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Behavioural Economics</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fast statistics </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Immoderate, intuitive, visceral, and powerful.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Behavioural Economics</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Slow statistics</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Thoughtful gathering of unbiased information.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Behavioural Economics</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Truth-default theory </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>54% accurate identifying liar. We can identify truth tellers far more easily, bad at identifying liars. We start in a default position of believing people and only when substantial evidence to the contrary presents itself do we change our position. In fact, we can even trivialize information away that in hindsight it rather pertinent. In a social experiment, teacher leaves room, answers are available, rando we've never met encouraging us to cheat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Behavioural Economics</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Illusion of Asymmetric Insights</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Belief that we know others better than they know us and that we may have insights about them that they lack (but not vice versa). As explained by the fill in the blanks word game, the words don't define me, yet they do define others. CIA Officers. Judges. </t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Behavioural Economics</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Intertemporal choice</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Refers to decisions that involve trade-offs between costs and benefits occurring at different points in time</t>
-        </is>
-      </c>
-    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -694,78 +674,188 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Fast statistics </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Immoderate, intuitive, visceral, and powerful.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Slow statistics</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Thoughtful gathering of unbiased information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Truth-default theory </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>54% accurate identifying liar. We can identify truth tellers far more easily, bad at identifying liars. We start in a default position of believing people and only when substantial evidence to the contrary presents itself do we change our position. In fact, we can even trivialize information away that in hindsight it rather pertinent. In a social experiment, teacher leaves room, answers are available, rando we've never met encouraging us to cheat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Illusion of Asymmetric Insights</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Belief that we know others better than they know us and that we may have insights about them that they lack (but not vice versa). As explained by the fill in the blanks word game, the words don't define me, yet they do define others. CIA Officers. Judges. </t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Intertemporal choice</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Refers to decisions that involve trade-offs between costs and benefits occurring at different points in time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Behavioural Economics</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Motivated reasoning</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Cognitive phenomenon where people process information in a biased way to support their existing beliefs, desires, or emotions. Instead of evaluating evidence objectively, individuals interpret information in a way that aligns with their preferred conclusions or outcomes. Directional reasoning: When people want to arrive at a specific conclusion, they give more weight to evidence that supports their desired belief and discount or dismiss evidence that contradicts it. Accuracy reasoning: In contrast, this occurs when individuals are genuinely motivated to arrive at a correct or objective conclusion. They carefully analyze all available evidence regardless of whether it supports their initial belief. 
 Type of cognitive bias where people process information in a way that aligns with their preexisting beliefs, desires, or emotions, rather than objectively evaluating the facts</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Behavioural Economics</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Naive realism</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Naïve realism is a concept from social psychology and philosophy that describes the human tendency to believe that we see the world objectively, and that other people who disagree must be uninformed, irrational, or biased.  
 Naïve realism explains why disagreements can become hostile. We assume others are irrational or malicious instead of recognizing legitimate differences in perspective or interpretation. It makes it harder to understand or appreciate others’ viewpoints, since we believe our view is the only valid one.It contributes to us-vs-them mentalities in politics and culture. Each side thinks it's simply seeing "facts," while the other is deluded.In workplaces or teams, naïve realism can block constructive dialogue and creative problem-solving by dismissing dissenting ideas too quickly.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Behavioural Economics</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Ostrich Effect</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>cognitive bias where people avoid information they perceive as potentially unpleasant or negative—like an ostrich metaphorically "burying its head in the sand" to avoid danger (even though real ostriches don't actually do this).</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Behavioural Economics</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Information</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>What Meaning Does a KPI actually have?</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Before we figure out whether nurses have had a pay raise, first find out what is meant by “nurse.” 
 Before lamenting the prevalence of self-harm in young people, stop to consider whether you know what “self-harm” is supposed to mean. Before concluding that inequality has soared, ask, “Inequality of what?” Demanding a short, sharp answer to the question “Has inequality risen?” is not only unfair, but strangely incurious. If we are curious instead, and ask the right questions, deeper insight is within easy reach.
@@ -774,90 +864,90 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Behavioural Economics</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Information</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Organizations</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t xml:space="preserve"> Great at solving Problems. Bad at diagnosing problems. 
 You should never trust large organizations, on the best day they’re incompetent, on a bad day they’re crooked.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Behavioural Economics</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Information</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Think about the Medium</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Weekly, daily, hourly—the metronome of the news clock changes the very nature of what is news. Daily news always seems more informative than rolling news; weekly news is typically more informative than daily news.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Behavioural Economics</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Information</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Unintended Consequences KPIs</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Must consider what adverse effects one might create when measuring. Doctors won't operate on sick patients. Data needs to be understood. Maximum day wait for appointment, doctors stopped taking appointments.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Behavioural Economics</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Information</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Facts Vs Statistics</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>More likely to die in accident in evening than in morning. More drivers in evening than in morning.
 More likely to die in clear weather than fog. More time occurs without fog, what does it actually mean???
@@ -867,219 +957,113 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Behavioural Economics</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Information</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Fact Believability</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Facts about this epidemic that have lasted a few days are far more reliable than the latest ‘facts’ that have just come out, which may be erroneous or unrepresentative and thus misleading . . . a question that today can be answered [by] only informed belief may perhaps be answered with a fact tomorrow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Bias, Fairness, and Ethics</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Bias, Fairness, and Ethics</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Review Demographics</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Evaluate model performance across key demographic or operational groups. Identifies potential unfair or unequal outcomes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Bias, Fairness, and Ethics</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Test unitended discrimination</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Review sensitive features and proxy variables. Prevents unintended discrimination.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Bias, Fairness, and Ethics</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Document Fairness Checks</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Document fairness checks and mitigation steps. Supports transparency, accountability, and compliance.</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cardinal Communication Sins</t>
+          <t>Behavioural Economics</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Fact Believability</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Facts about this epidemic that have lasted a few days are far more reliable than the latest ‘facts’ that have just come out, which may be erroneous or unrepresentative and thus misleading . . . a question that today can be answered [by] only informed belief may perhaps be answered with a fact tomorrow.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cardinal Communication Sins</t>
+          <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Deliver Simplicity</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Do not make the user think</t>
+          <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cardinal Communication Sins</t>
+          <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Do Not Demand Recall</t>
+          <t>Review Demographics</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Do not make the user remember. If the Speaker utters 120 word a minute, the audience is thinking 500.</t>
+          <t>Evaluate model performance across key demographic or operational groups. Identifies potential unfair or unequal outcomes.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cardinal Communication Sins</t>
+          <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Visuals in 2D</t>
+          <t>Test unitended discrimination</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Do not use 3D unless absolutely necessary.</t>
+          <t>Review sensitive features and proxy variables. Prevents unintended discrimination.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cardinal Communication Sins</t>
+          <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avoid Pie Charts</t>
+          <t>Document Fairness Checks</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Pie Charts. They Suck.</t>
+          <t>Document fairness checks and mitigation steps. Supports transparency, accountability, and compliance.</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1075,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Warning</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Do Not Offend Your Audience</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1114,10 +1098,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Do Not Let Predjudices Close Your Mind</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Deliver Simplicity</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Do not make the user think</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1132,10 +1120,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Don’t waste the advantage that thought has over speech</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Do Not Demand Recall</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Do not make the user remember. If the Speaker utters 120 word a minute, the audience is thinking 500.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1150,12 +1142,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hearing vs Listening</t>
+          <t>Visuals in 2D</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Most were born hearing well, EVERYONE must learn to listen well.</t>
+          <t>Do not use 3D unless absolutely necessary.</t>
         </is>
       </c>
     </row>
@@ -1172,47 +1164,47 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Always Thank Your Audience</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Avoid Pie Charts</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pie Charts. They Suck.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Choosing a Medium</t>
+          <t>Cardinal Communication Sins</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>While not always give a choice, it is important to be mindful that the ability to communicate, in terms of breadth, depth, clarity and pursuaiveness differ across mediums, so one must be plan and execute accordingly. Additional there might be a preference/ opportunity to advocate for a distinct and preferred medium.</t>
-        </is>
-      </c>
+          <t>Do Not Offend Your Audience</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Cardinal Communication Sins</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Definition</t>
+          <t>Do Not Let Predjudices Close Your Mind</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1220,17 +1212,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Cardinal Communication Sins</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Understand Your Message</t>
+          <t>Don’t waste the advantage that thought has over speech</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1238,57 +1230,57 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Cardinal Communication Sins</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Understand Your Audience</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Hearing vs Listening</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Most were born hearing well, EVERYONE must learn to listen well.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Cardinal Communication Sins</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Warning</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Understand Your Strategy</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Beyond understanding Your Message, you need to think about how you are going to articulate your story, your goals, motivation, priority. Reconizing differences between things that have great personal meaning, business relevance, or simply mandated work.</t>
-        </is>
-      </c>
+          <t>Always Thank Your Audience</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Choosing a Medium</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Choosing a Medium</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1305,12 +1297,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Understand Your Visuals</t>
+          <t>Definition</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1328,14 +1320,10 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Message Spareness</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Utilize a less is more approach, whether that is Slides, Words, Pages, Etc. Less is more.</t>
-        </is>
-      </c>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1345,15 +1333,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Understand Your Message</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Re-enforce the Message</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>Do not Assume it is Dull.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Even if it might be less than impressive, or revolutionary for you, do not convey this.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1363,15 +1355,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Understand Your Message</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cardinal Communication Sins</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>Do you actually understand it?</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>You must understand it, backforward and center. Message, Purpose. Reason. All can be different, might have different motivations.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1381,17 +1377,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cardinal Communication Sins</t>
+          <t>Understand Your Message</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Deliver Simplicity</t>
+          <t>Clarity for all.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Do not make the user think</t>
+          <t>Is the message clear to you, will it be clear to them?</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1399,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cardinal Communication Sins</t>
+          <t>Understand Your Message</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Do Not Demand Recall</t>
+          <t>BLUF</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Do not make the user remember. If the Speaker utters 120 word a minute, the audience is thinking 500.</t>
+          <t>Bottom Line Up Front</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1421,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cardinal Communication Sins</t>
+          <t>Understand Your Message</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Visuals in 2D</t>
+          <t>Tell the Story, Do not Show it.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Do not use 3D unless absolutely necessary.</t>
+          <t>Storytelling beats data 100% of the time.</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1443,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cardinal Communication Sins</t>
+          <t>Understand Your Message</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avoid Pie Charts</t>
+          <t>Where are you truly at?</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Pie Charts. They Suck.</t>
+          <t>Is the glass half full, half empty. If it's half full, do you have what you really want in the glass?</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1465,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cardinal Communication Sins</t>
+          <t>Process Step</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Do Not Offend Your Audience</t>
+          <t>Understand Your Audience</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -1487,15 +1483,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cardinal Communication Sins</t>
+          <t>Understand Your Audience</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Do Not Let Predjudices Close Your Mind</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Who is it?</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>It might be extremely broad, it might change for a similiar piece of work, or the work might be done with a single person in mind, and little focus or regard is paid to others, regardless of the level of interaction to which they will have.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1505,15 +1505,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cardinal Communication Sins</t>
+          <t>Understand Your Audience</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Don’t waste the advantage that thought has over speech</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>What do they want?</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The more we know about the motivations and incentives of decision makers, the more we can control the communication. </t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1523,19 +1527,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cardinal Communication Sins</t>
+          <t>Understand Your Audience</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hearing vs Listening</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Most were born hearing well, EVERYONE must learn to listen well.</t>
-        </is>
-      </c>
+          <t>Are they likely to Care?</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1545,15 +1545,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cardinal Communication Sins</t>
+          <t>Understand Your Audience</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Always Thank Your Audience</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Getting CEO to Pick</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>How to get a CEO to remove a soft drink from Japan without telling them to remove a soft drink from Japan.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1563,15 +1567,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Understand Your Audience</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>General Expectations</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Stress Induced U Curve</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>High Pressure Decision Making: The inverted U shape Curve, Stress vs Performance. No one knows exactly where it is for each individual.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1581,148 +1589,764 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Process Step</t>
+          <t>Understand Your Audience</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Measuing Effectiveness</t>
+          <t>Cuban Missile Crisis</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>How can one measure how effective/ineffective a particular communication was?</t>
+          <t>Asymmetric Information, Deception, Misreading Adversarial Strength, Attempting to disrupt competitor. Fear is the reigning notion. People don't read the data well when fear is involved.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Understand Your Strategy</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Beyond understanding Your Message, you need to think about how you are going to articulate your story, your goals, motivation, priority. Reconizing differences between things that have great personal meaning, business relevance, or simply mandated work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Choosing a Medium</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>While not always give a choice, it is important to be mindful that the ability to communicate, in terms of breadth, depth, clarity and pursuaiveness differ across mediums, so one must be plan and execute accordingly. Additional there might be a preference/ opportunity to advocate for a distinct and preferred medium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Understand Your Visuals</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Understand Your Visuals</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Interesting and Engaging Visuals, Minimal Words.</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>80% Salient might be better than 100% accurate</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Understand Your Visuals</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Simplicity over Complexity</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Are they Simple and Clear?</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Understand Your Visuals</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Will they understand?</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>People are easily distractible, so they might not recognize stuff that is immediately in front of them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Understand Your Visuals</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Eyes Not Minds</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Message Spareness</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Utilize a less is more approach, whether that is Slides, Words, Pages, Etc. Less is more.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Re-enforce the Message</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Deliver Simplicity</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Do not make the user think</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Do Not Demand Recall</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Do not make the user remember. If the Speaker utters 120 word a minute, the audience is thinking 500.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Visuals in 2D</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Do not use 3D unless absolutely necessary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Avoid Pie Charts</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Pie Charts. They Suck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Do Not Offend Your Audience</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Do Not Let Predjudices Close Your Mind</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Don’t waste the advantage that thought has over speech</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Hearing vs Listening</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Most were born hearing well, EVERYONE must learn to listen well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Cardinal Communication Sins</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Always Thank Your Audience</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>General Expectations</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Measuing Effectiveness</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>How can one measure how effective/ineffective a particular communication was?</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Persuasion</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Persuasion</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Reciprocity</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>People say yes to those who said yes to them. Invest in those you want to invest in you. Be the first to give, and do it personalized and unexpected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Persuasion</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Scarcity</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>People want what is in short supply. Tell them what they gain, what is unique and what they stand to lose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Persuasion</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Authority</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Make sure people know your expertise. Don't be arrogant. Specifically if they don't know you, get a third party to introduce you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Persuasion</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Consistency</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>People like to be consistent when they take a public opinion. Get them to take a small step first, then they will be willing to take a big step in the future.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Persuasion</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Liking</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>People want to be liked and work with people who like them. We like people who are similar to us, compliment us, cooperate with us</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Persuasion</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Consensus</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>People follow the leads of others.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
         <is>
           <t>Label Data</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>Ensure that All data is defined, and classified. Including Semantic and Functional Definitions.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
         <is>
           <t>Ensure Sufficient Data Exists</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>Ensure that model has sufficient representation (Covered from at a Minimum Semantic and Functional Perspective).</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>Warning</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Challenges from Missing Data</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t xml:space="preserve">What concessions have we made due to a lack of data availability, and how are those going to undermine the work we plan on doing. </t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>Consideration</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Who Owns the Data</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Who is the Data Steward, and Process owners? Are they and have they been involved. Operationally do we have integrity, consistency and availability to include?</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Data Engineering</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Data Engineering</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Wall vs Process Time</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Must consider what you are actually attempting to measure, Wall Time helps to under from User Experience, Process Time more so from a resource and cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
 Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
@@ -1730,509 +2354,721 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
         <is>
           <t>Regularization</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>Explain what this means from a practical application of what needs to be done for the proces.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Regularization</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>ElasticNet</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>Approach which combines L1 and L2 Regularization.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>Regularization</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the absolute values of the coefficients as a penalty term. This leads to sparse models, as some coefficients become exactly zero</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>Regularization</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the squared values of the coefficients as a penalty term. This increases the cost of larger parameters, encouraging the model to distribute parameters waiting This shrinks the coefficients but does not eliminate them.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Identify Criteria</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Always identify multiple criteria, how can we fairly compare approaches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Identify Evaluation Framework</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Small vs Big Decisions</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Big decision which occur less frequently requre a different level of discernment than small decisions which occur frequently, specifically skills, information and situation all vary greatly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>How do Emotions Impact</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Our emotions, preconceptions, political affiliations badly wrap the way we interpret evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>How individuals choose</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Don't convince smokers cigarettes aren't bad, just that the evidence which suggested they were dangerous was questionable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>How does bias influence?</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Biases appear negatively. People can argue against what they don't like.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>How to Change Perspective.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Statistics show us things we can’t see in any other way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Why are we collecting data?</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>We depend on reliable data to shape our decisions. Often only collect in the face of adversity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Decision Making</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Choice is Hard..</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Offering more choices sometimes motivates and sometimes demotivates people.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
         <is>
           <t>Package Model for Deployment with everything necessary</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>Package the model with all required preprocessing steps. Ensures predictions in production match training conditions.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
         <is>
           <t>Test in different environments</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>Test the model in a staging or test environment. Utilize Dedicated Environment. Reduces risk of failures in production.</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
         <is>
           <t>Version Control</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>Create a versioned and reproducible deployment artifact. Supports rollback, auditing, and maintenance.</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>Exploratory Data Analysis</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
         <is>
           <t>Ratios or Observed Values</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>What ratios or proportions could better represent behavior than raw values? Many real-world patterns depend on relative size (e.g., debt-to-income, usage-to-capacity), so ratios often reveal signal that absolute values hide.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
         <is>
           <t>Include Interactions</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>What combinations or interactions might reflect how factors work together? Some outcomes are driven by the interaction between variables (e.g., high balance and high transaction frequency), so combining features can expose relationships a model might miss.</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
         <is>
           <t>How does Time Impact?</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>What time-based changes or aggregates could capture trends or stability? Differences, growth rates, or rolling averages often reflect momentum or consistency, which are strong predictors of future behavior.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
         <is>
           <t>Explain Feature Practical Relevance</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>Generate feature importance or explanation outputs. Helps understand what drives model predictions.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
         <is>
           <t>Remove Unnecessary Features</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>Remove features with high missingness or low variance. Reduces noise and improves model stability.</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
         <is>
           <t>Understand Feature Correlations</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>Check for multicollinearity or redundant features. Helps prevent unstable models and improves interpretability.</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
         <is>
           <t>Document Feature Statistical Relevance</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>Validate selected features using model or statistical methods. Ensures the retained features actually contribute to predictive performance.</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>Warning</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>Avoid Ambguity</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>Avoid ambiguous features. Is a Banana ripe, who says so?</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>Warning</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>Is a feature Random?</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>Careful when something is truly random generated, Atmospheric Change, Earthquakes, Stocks. Very difficult, if not impossible to predict.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B123" t="inlineStr">
         <is>
           <t>Warning</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>Model Robustness</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>How robust is your model to change and what is it actually predicting.  MNIST performance when tilting Images, of adding noise.</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
         <is>
           <t>Test Individual Feature Importance</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>Need to understand how much an individual feature contributes beyond what the other features already provide. A feature has incremental value and removing or disrupting it should decrease performance. This supports inclusion of value add feature, opposed to those which create redundancy or noise.</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="125">
+      <c r="A125" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
         <is>
           <t>Reconstruction Error in Autoencoders</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>Does this feature improve the model’s ability to represent and reconstruct the data? An autoencoder learns to compress the input data into a smaller latent representation and then reconstruct the original data. Reconstruction error measures the difference between the original observations and the reconstructed output; lower error generally means the model has preserved more of the data’s structure.
 For feature selection, you can remove, mask, or add one feature at a time and observe how reconstruction error changes. A substantial increase in error after removing a feature suggests that the feature contains important information, although highly correlated features may appear less important because another feature can reconstruct the same information.
@@ -2240,23 +3076,23 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="126">
+      <c r="A126" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
         <is>
           <t>Mutual Information with Latent Cluster Assignment</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>How strongly is this feature associated with the cluster structure the model discovered? Mutual information measures how much knowing one variable reduces uncertainty about another. In this context, it measures the association between a feature and the cluster labels produced by an unsupervised model.
 For feature selection, features with high mutual information are strongly associated with the discovered cluster structure and may be useful for distinguishing groups. Features with very low mutual information may contribute little to the final segmentation, although they could still affect the clustering indirectly through interactions with other features.
@@ -2264,23 +3100,23 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="127">
+      <c r="A127" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
         <is>
           <t>Permutation for Clustering</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>Permutation importance measures the value of a feature by randomly shuffling its values while leaving the other features unchanged. Shuffling breaks the feature’s relationship with the observations; if cluster quality, assignment consistency, or model performance worsens, the feature was contributing useful information.
 For feature selection, features that cause a large decline in clustering performance when shuffled are considered important. Features whose permutation has little effect may be redundant, irrelevant, or dominated by stronger features and could be candidates for removal.
@@ -2289,903 +3125,903 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>Baseline represents the typical or expected behavior of an entity over a meaningful historical period. It answers the question “What is normal for this entity?” and provides context against which current state and changes can be interpreted. Baseline is conceptually stable even when its numeric value evolves, allowing models to distinguish structural differences between entities from temporary deviations. In modeling, Baseline is often foundational for defining identity and long-term segmentation.</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Dimension</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>A Dimension is a conceptual axis of behavior or meaning that you believe exists in the real world and want your model to represent. It answers a behavioral or semantic question, not a technical one. Dimensions are stable over time, even as data sources, features, or models change (for example, we always need to understand Current State, and rate of change, even though both of what is being studied may change drastically). They are the why behind your features.
 Ultimately, it is the question, What Behaviour Matters.</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>Implementation</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>An Implementation is a specific measurable representation of a dimension, derived from available data. It answers the question: “How is this dimension measured in practice?” Implementations operationalize a dimension through a defined calculation, methodology, or analytical approach. While implementations may evolve as data quality, availability, or methodology improves, they should always map clearly back to a single dimension.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>Momentum</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>Momentum represents the direction and rate of change in behavior over time. It answers the question “Is this entity increasing, decreasing, or remaining stable?” and captures transitional dynamics that are not visible from state or baseline alone. Momentum is critical for detecting emerging trends, shifts in behavior, and potential future movement between segments. In modeling, Momentum often explains why change is occurring rather than what the current condition is.</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>A Parameter is a tuning choice that controls how an implementation is calculated, without changing what it represents. Parameters affect sensitivity, smoothness, or scale, but not conceptual meaning. They are the knobs you turn during experimentation. Examples include Window length: 3M vs 6M vs 12M, Weighting scheme: equal vs exponential, Aggregation: mean vs median
 Ultimately it is the questions, How do we compute it.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>General Definition</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Volatility</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>Volatility represents the consistency or variability of behavior over time. It answers the question “How stable or predictable is this entity’s behavior?” and distinguishes steady patterns from irregular or erratic ones. Volatility provides important diagnostic context, helping differentiate sustained change from noise or one-off events. In modeling, Volatility is typically explanatory or risk-related rather than defining core identity.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>General Expectations</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="D134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>Specific</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="137">
+      <c r="A137" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>Measurable</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>Achievable</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+    <row r="139">
+      <c r="A139" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>Relevant</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>Time Bound</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>Hyperparameter Tuning</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>Hyperparameter Tuning</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
         <is>
           <t>Define Search Space</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>Define a clear search space for key hyperparameters. Ensures tuning focuses on meaningful configurations.</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>Hyperparameter Tuning</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
         <is>
           <t>Cross Validation to Prevent Overfitting</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>Use cross-validation or a validation set for tuning. Prevents overfitting to the training data.</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>Hyperparameter Tuning</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
         <is>
           <t>Document Results</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>Record best parameters and associated performance. Allows reproducibility and comparison across experiments.</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>Hyperparameter Tuning</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
         <is>
           <t>Explicit Exploration. Avoid needless and endless tuning</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>Define Parameters you will tune and approach to tuning before you commence tuning. Do not simply tune model to optimal parameters without considering what you are actually doing, and its ability to generalize.</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>To Be Defined</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>Thought process utilized to establish a clear, concise and explicit goal. While ideally the goal will be defined in terms of Key Performance Indicators, when the work is explorative or borne in the spirit of experimentation it is still critical to establish guardrails, and start from a place of consensus among stakeholders.  There should be no more than 3 Goals (Flexible), the goals should be SMART and explicitly acknowledged and the distinction of whether something actually meets the criteria (and whether it was successful) should be clear.</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>Specific</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>Describes what will be accomplished and what success will look like. It answers the questions: What will I do? Who is involved? What area am I focusing on? The more precise the goal, the easier it is to plan actions and stay focused.</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>Measurable</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>Includes a clear way to track progress or determine success. This may involve numbers, percentages, milestones, deliverables, or observable outcomes. Measurement ensures accountability and helps you know when the goal has been achieved.</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>Achievable</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>Realistic given available time, resources, skills, and competing priorities. It should stretch performance but still be possible to accomplish with focused effort. Setting achievable goals helps maintain motivation and builds confidence through success.</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>Relevant</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>Aligns with broader priorities, such as team objectives, organizational strategy, or personal development plans. It should contribute meaningful value rather than being an isolated or low-impact task. Relevance ensures time and energy are spent on what matters most.</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
         <is>
           <t>Goal Setting</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>Time Bound</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>Includes a clear deadline or timeframe for completion. This creates urgency, supports planning, and prevents goals from being postponed indefinitely. Defined timelines also make it easier to monitor progress and adjust actions if needed.</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D153" t="inlineStr">
         <is>
           <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>Desired State Metrics</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D154" t="inlineStr">
         <is>
           <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>Current State Analysis</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D155" t="inlineStr">
         <is>
           <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>Root Cause Assessment</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D156" t="inlineStr">
         <is>
           <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>Historical Overview</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D157" t="inlineStr">
         <is>
           <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>Baseline Metrics (Current State)</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D158" t="inlineStr">
         <is>
           <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C159" t="inlineStr">
         <is>
           <t>Understand KPIs which are meaningful.</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D159" t="inlineStr">
         <is>
           <t>Attempt to explicitly define outcomes and relevant KPIs for those outcomes. Where that can not happen, it is important to understand why that can not happen. What is happening if we don't have and follow metrics. IE. The Account Opening Process is not efficient and needs to improve, The Internet Banking Experience is poor, and does not attract customers. How do you monitor this, how can you define this, how can you prove this,  how do you expect this to change and measure that change.
 How will the project and efforts be measured where success can not be objectively measured? How will resources be allocated when it remains unclear what benefit or risk exists.</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>What Lens is Problem Defined?</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>Must be careful at how problem is defined. Is it defined in the context of the already identified solution, has it been validated and is the problem distinct from the analysis and potential solution, or have we leaked into the process.</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>Stakeholder Investment?</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>How Invested are stakeholders in defining the problem? What is their view of the process/ project, how invested, interested and engaged are they. What are their personal goals and motivation, speed, accuracy, validation of ideology?</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C162" t="inlineStr">
         <is>
           <t>Really Understand Problem Statement</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D162" t="inlineStr">
         <is>
           <t>Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk and the likelihood of not meeting expectations, frustration, or material change to purpose, scope or priority is inevitable.</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
         <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D163" t="inlineStr">
         <is>
           <t>Data collection involves identifying, sourcing, and acquiring the datasets required to solve the defined problem. This may include internal databases, APIs, logs, third-party data, or manually collected data. Key considerations include data availability, coverage, granularity, freshness, and legal or privacy constraints. The quality and relevance of collected data fundamentally limit the ceiling of model performance.
 Need to understand the data available to solve a problem, insure that it's documented, understood and trusted. Need to identify, not only information which is available, but information which is not available and should be.  This should be explicitly documented, referenced constantly and readily available (Semantic and Functional Definition).</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
         <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>Label Data</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>Ensure that All data is defined, and classified. Including Semantic and Functional Definitions.</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
         <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C165" t="inlineStr">
         <is>
           <t>Ensure Sufficient Data Exists</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>Ensure that model has sufficient representation (Covered from at a Minimum Semantic and Functional Perspective).</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
         <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C166" t="inlineStr">
         <is>
           <t>Challenges from Missing Data</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t xml:space="preserve">What concessions have we made due to a lack of data availability, and how are those going to undermine the work we plan on doing. </t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
         <is>
           <t>Data Collection</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C167" t="inlineStr">
         <is>
           <t>Who Owns the Data</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D167" t="inlineStr">
         <is>
           <t>Who is the Data Steward, and Process owners? Are they and have they been involved. Operationally do we have integrity, consistency and availability to include?</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D168" t="inlineStr">
         <is>
           <t>Data preparation focuses on cleaning and structuring raw data into a usable format for modeling. This includes handling missing values, correcting errors, standardizing formats, encoding categorical variables, and aligning labels with features. It also often involves train/validation/test splitting to prevent data leakage. This step is critical because most models assume clean, well-structured inputs and are highly sensitive to data issues.
 Need to establish up a consistent, robust and repeatable data ingestion process, which starts at the outset of the project. Where the infrastructure is not immediately available, need to clearly document the journey.  Need to call out requirements, expectations and limitations, and where resources are necessary, they should be identified at this point. 
@@ -3193,421 +4029,421 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>Regularization</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D169" t="inlineStr">
         <is>
           <t>Explain what this means from a practical application of what needs to be done for the proces.</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
         <is>
           <t>Regularization</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C170" t="inlineStr">
         <is>
           <t>ElasticNet</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D170" t="inlineStr">
         <is>
           <t>Approach which combines L1 and L2 Regularization.</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
         <is>
           <t>Regularization</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D171" t="inlineStr">
         <is>
           <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the absolute values of the coefficients as a penalty term. This leads to sparse models, as some coefficients become exactly zero</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
         <is>
           <t>Regularization</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D172" t="inlineStr">
         <is>
           <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the squared values of the coefficients as a penalty term. This increases the cost of larger parameters, encouraging the model to distribute parameters waiting This shrinks the coefficients but does not eliminate them.</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
         <is>
           <t>Exploratory Data Analysis</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D173" t="inlineStr">
         <is>
           <t xml:space="preserve">Foundational step in ensuring the success of a machine learning model—and, by extension, the overall project. Its purpose is to confirm that the data is appropriately structured, consistent, and of sufficient quality to support reliable modeling.
 While every dataset and project is unique, applying a consistent EDA approach helps reduce the laborious and time-consuming nature of data preparation. A structured process enables quicker identification of data issues, improves understanding of key variables and relationships, and creates a more stable foundation for subsequent modeling decisions. </t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D174" t="inlineStr">
         <is>
           <t>Process of creating new input variables that better represent the underlying patterns in the data. It may include transformations (log, scaling), aggregations, interactions, temporal features, or domain-specific encodings. Effective feature engineering can significantly improve model performance even with simple algorithms. It embeds domain knowledge into the model and often provides more value than algorithmic complexity.  It is often one of the most impactful steps in the machine learning workflow.</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>Ratios or Observed Values</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D175" t="inlineStr">
         <is>
           <t>What ratios or proportions could better represent behavior than raw values? Many real-world patterns depend on relative size (e.g., debt-to-income, usage-to-capacity), so ratios often reveal signal that absolute values hide.</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>Include Interactions</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>What combinations or interactions might reflect how factors work together? Some outcomes are driven by the interaction between variables (e.g., high balance and high transaction frequency), so combining features can expose relationships a model might miss.</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
         <is>
           <t>Feature Engineering</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>How does Time Impact?</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>What time-based changes or aggregates could capture trends or stability? Differences, growth rates, or rolling averages often reflect momentum or consistency, which are strong predictors of future behavior.</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D178" t="inlineStr">
         <is>
           <t>Process of identifying and retaining the most relevant variables for model training while removing redundant, noisy, or irrelevant features. This helps reduce overfitting, improve model performance, and increase interpretability. Feature selection techniques may be statistical, model-based, or embedded within the learning algorithm. The goal is to create a simpler, more robust feature set that generalizes well to new data.
 It is important to be in a position to Logically and Mathematically be in a position to defend inclusion and exclusion decisions. Although a highly technical step, it is critically important that stakeholders and partners are included and in references and terms which are appropriate for them.</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C179" t="inlineStr">
         <is>
           <t>Explain Feature Practical Relevance</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D179" t="inlineStr">
         <is>
           <t>Generate feature importance or explanation outputs. Helps understand what drives model predictions.</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>Remove Unnecessary Features</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D180" t="inlineStr">
         <is>
           <t>Remove features with high missingness or low variance. Reduces noise and improves model stability.</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>Understand Feature Correlations</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D181" t="inlineStr">
         <is>
           <t>Check for multicollinearity or redundant features. Helps prevent unstable models and improves interpretability.</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>Document Feature Statistical Relevance</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D182" t="inlineStr">
         <is>
           <t>Validate selected features using model or statistical methods. Ensures the retained features actually contribute to predictive performance.</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C183" t="inlineStr">
         <is>
           <t>Avoid Ambguity</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D183" t="inlineStr">
         <is>
           <t>Avoid ambiguous features. Is a Banana ripe, who says so?</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
+      <c r="C184" t="inlineStr">
         <is>
           <t>Is a feature Random?</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D184" t="inlineStr">
         <is>
           <t>Careful when something is truly random generated, Atmospheric Change, Earthquakes, Stocks. Very difficult, if not impossible to predict.</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="C185" t="inlineStr">
         <is>
           <t>Model Robustness</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D185" t="inlineStr">
         <is>
           <t>How robust is your model to change and what is it actually predicting.  MNIST performance when tilting Images, of adding noise.</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="C186" t="inlineStr">
         <is>
           <t>Test Individual Feature Importance</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D186" t="inlineStr">
         <is>
           <t>Need to understand how much an individual feature contributes beyond what the other features already provide. A feature has incremental value and removing or disrupting it should decrease performance. This supports inclusion of value add feature, opposed to those which create redundancy or noise.</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
+      <c r="C187" t="inlineStr">
         <is>
           <t>Reconstruction Error in Autoencoders</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D187" t="inlineStr">
         <is>
           <t>Does this feature improve the model’s ability to represent and reconstruct the data? An autoencoder learns to compress the input data into a smaller latent representation and then reconstruct the original data. Reconstruction error measures the difference between the original observations and the reconstructed output; lower error generally means the model has preserved more of the data’s structure.
 For feature selection, you can remove, mask, or add one feature at a time and observe how reconstruction error changes. A substantial increase in error after removing a feature suggests that the feature contains important information, although highly correlated features may appear less important because another feature can reconstruct the same information.
@@ -3615,23 +4451,23 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C188" t="inlineStr">
         <is>
           <t>Mutual Information with Latent Cluster Assignment</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D188" t="inlineStr">
         <is>
           <t>How strongly is this feature associated with the cluster structure the model discovered? Mutual information measures how much knowing one variable reduces uncertainty about another. In this context, it measures the association between a feature and the cluster labels produced by an unsupervised model.
 For feature selection, features with high mutual information are strongly associated with the discovered cluster structure and may be useful for distinguishing groups. Features with very low mutual information may contribute little to the final segmentation, although they could still affect the clustering indirectly through interactions with other features.
@@ -3639,23 +4475,23 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
         <is>
           <t>Feature Selection</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C189" t="inlineStr">
         <is>
           <t>Permutation for Clustering</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D189" t="inlineStr">
         <is>
           <t>Permutation importance measures the value of a feature by randomly shuffling its values while leaving the other features unchanged. Shuffling breaks the feature’s relationship with the observations; if cluster quality, assignment consistency, or model performance worsens, the feature was contributing useful information.
 For feature selection, features that cause a large decline in clustering performance when shuffled are considered important. Features whose permutation has little effect may be redundant, irrelevant, or dominated by stronger features and could be candidates for removal.
@@ -3664,218 +4500,218 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D190" t="inlineStr">
         <is>
           <t>The process of choosing the most appropriate algorithm or model type for a given problem and dataset. This decision is based on factors such as data size, feature structure, interpretability needs, computational constraints, and performance requirements. Multiple candidate models are often tested and compared using consistent evaluation methods. The objective is to identify the model that provides the best balance between accuracy, stability, and practical usability.
 Similar to the process of engagement and audit followed in Feature Selection, it is critically important that actions are documented, defensible and clearly and consistently articulated to stakeholders in a meaningful manner.</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C191" t="inlineStr">
         <is>
           <t>Define Baseline</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
+      <c r="D191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
+      <c r="C192" t="inlineStr">
         <is>
           <t>Document Results and Choice</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="D192" t="inlineStr">
         <is>
           <t>Ensure that final selection is documented and agreed by appropriate stakeholders, who have been part of entire development journey, understand and are aware.</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="C193" t="inlineStr">
         <is>
           <t>Define Validation Approach in Advance</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="D193" t="inlineStr">
         <is>
           <t>Use cross-validation or a structured validation approach. Provides a more reliable estimate of model performance.</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="C194" t="inlineStr">
         <is>
           <t>Validate no Leakage</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>Ensure no data leakage between training and validation sets. Prevents overly optimistic performance estimates.</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C195" t="inlineStr">
         <is>
           <t>Validate consistency over time</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="D195" t="inlineStr">
         <is>
           <t>Confirm performance stability across folds or time splits. Indicates the model is robust and generalizable.</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="C196" t="inlineStr">
         <is>
           <t>How will Model Learn?</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="D196" t="inlineStr">
         <is>
           <t>Must select an appropriate learning method. Supervised, Unsupervised, Semi-Supervised, Reinforcement</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="C197" t="inlineStr">
         <is>
           <t>What Problem is the Model Solving?</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="D197" t="inlineStr">
         <is>
           <t>Must select an appropriate method. Classification, Regression, Clustering, Dimensionality Reduction, etc.</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C198" t="inlineStr">
         <is>
           <t>What Model/Algo is being used to solve the problem</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D198" t="inlineStr">
         <is>
           <t>Document founational assessment at the outset, can revisit during Model Selection.</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C199" t="inlineStr">
         <is>
           <t>Select Model(s) based on Objective</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D199" t="inlineStr">
         <is>
           <t xml:space="preserve">Define what the objective of the model work is, state what is being measured and why. 
 Document all models which will be considered, including why they are appropriate and where models are excluded, insure rationale available. Compare multiple model types using the same validation approach. Ensures a fair comparison and better-informed model choice.
@@ -3883,1378 +4719,1490 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C200" t="inlineStr">
         <is>
           <t>Create and Understand Baseline</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D200" t="inlineStr">
         <is>
           <t>Create Simplified Baseline Model, use this are reference. Ensure that this is communicated to Stakeholders, so they understand both the benchmark and expectation, to determine relevance. Should align with Goals.</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="C201" t="inlineStr">
         <is>
           <t>Performance vs Cost vs Practicality</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D201" t="inlineStr">
         <is>
           <t>Consider interpretability, performance, and computational cost. Balances practical constraints with predictive accuracy.</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
+      <c r="C202" t="inlineStr">
         <is>
           <t>How Many Examples are Needed?</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="D202" t="inlineStr">
         <is>
           <t>Distinct for every type of Method or approach. Need to be comfortable that the dataset has enough examples and that they represent a population to which you believe is representive.</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C203" t="inlineStr">
         <is>
           <t>Understand what your model is actually solving and how.</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D203" t="inlineStr">
         <is>
           <t>Models will cheat and can solve problems which appear to be optimal, but they might not be solving what you expect or require, they might be finding patterns in the data which you do not see. An Example of this would a classification model with Wolves and Dogs,  many wolf photos happened to be taken in snowy environments, while dog photos were often taken indoors or on grass. The model learned to detect snow, not animals.</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C204" t="inlineStr">
         <is>
           <t>Speed vs Accuracy</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t>The most accurate model is not always the most valuable. Delivering a good solution quickly often creates more business value than spending significant time chasing small improvements in performance.</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
+      <c r="C205" t="inlineStr">
         <is>
           <t>Accuracy vs Repeatability</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D205" t="inlineStr">
         <is>
           <t>A highly accurate result has limited value if it cannot be reproduced consistently. Prioritize workflows, data pipelines, and model training processes that generate reliable and repeatable outcomes over one-time exceptional results.</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
+      <c r="C206" t="inlineStr">
         <is>
           <t>Correlation vs Causation</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="D206" t="inlineStr">
         <is>
           <t>Machine learning identifies relationships in data but does not prove why those relationships exist. Treat model outputs as evidence of association and rely on experimentation or domain expertise to establish causal conclusions.</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C207" t="inlineStr">
         <is>
           <t>Stability over Uniqueness</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D207" t="inlineStr">
         <is>
           <t>Prefer models that perform consistently across different datasets and over time rather than those that achieve exceptional results only under specific conditions. Reliable, generalizable models are more valuable than highly specialized ones that are difficult to maintain.</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="C208" t="inlineStr">
         <is>
           <t>Interpretability over Novelty</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="D208" t="inlineStr">
         <is>
           <t>A simple model that stakeholders understand and trust is often more useful than a complex state-of-the-art model with marginal performance gains. Choose complexity only when it delivers meaningful improvements that justify reduced transparency.</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>Repeatability over Perfection</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
+      <c r="D209" t="inlineStr">
         <is>
           <t>Machine learning is an iterative process, not a search for a flawless model. Build solutions that others can rerun, validate, and improve, knowing that incremental refinement typically delivers more long-term value than pursuing perfection from the outset.</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="C211" t="inlineStr">
         <is>
           <t>Train, Test, Validation Split</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="D211" t="inlineStr">
         <is>
           <t>Is split between Training, Testing and Validation appropriate, fair and responsible. Validate and document.</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="C212" t="inlineStr">
         <is>
           <t>Convergence Achieved?</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="D212" t="inlineStr">
         <is>
           <t>Verify model converges and loss decreases during training. Confirms the model is learning meaningful patterns.</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
+      <c r="C213" t="inlineStr">
         <is>
           <t>Logging of Parameters</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>Log model parameters, features, training configuration and results. Supports reproducibility and troubleshooting.</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Activation Function</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Select a Activation Function based on Learning Paradigm and Method, potentially trying multiple variants across grid search.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Activation Function</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Leaky Relu</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Activation Function</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Relu</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Activation Function</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Sigmoid</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Activation Function</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Softmax</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Activation Function</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Tanh</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
         <is>
           <t>Any dataset can be optimized</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>Any data set can be optimized, even when there is NO relation it will generalize. Remember the goal, ability to generalize, not simply predict training.</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
         <is>
           <t>Hyperparameter Tuning</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>Optimizing the configuration settings that control how a model learns, rather than the parameters learned during training. These settings, such as tree depth or regularization strength, can significantly influence model performance and stability. Tuning is typically done using methods like grid search, random search, or Bayesian optimization. The goal is to identify the hyperparameter combination that produces the best validation performance.</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
         <is>
           <t>Hyperparameter Tuning</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
+      <c r="C222" t="inlineStr">
         <is>
           <t>Define Search Space</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="D222" t="inlineStr">
         <is>
           <t>Define a clear search space for key hyperparameters. Ensures tuning focuses on meaningful configurations.</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
         <is>
           <t>Hyperparameter Tuning</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="C223" t="inlineStr">
         <is>
           <t>Cross Validation to Prevent Overfitting</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>Use cross-validation or a validation set for tuning. Prevents overfitting to the training data.</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
         <is>
           <t>Hyperparameter Tuning</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="C224" t="inlineStr">
         <is>
           <t>Document Results</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D224" t="inlineStr">
         <is>
           <t>Record best parameters and associated performance. Allows reproducibility and comparison across experiments.</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
         <is>
           <t>Hyperparameter Tuning</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
+      <c r="C225" t="inlineStr">
         <is>
           <t>Explicit Exploration. Avoid needless and endless tuning</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="D225" t="inlineStr">
         <is>
           <t>Define Parameters you will tune and approach to tuning before you commence tuning. Do not simply tune model to optimal parameters without considering what you are actually doing, and its ability to generalize.</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
         <is>
           <t>Model Evaluation</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
         <is>
           <t>Model Evaluation</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="C227" t="inlineStr">
         <is>
           <t>Test Relative to Baseline</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
+      <c r="D227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
         <is>
           <t>Model Evaluation</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C228" t="inlineStr">
         <is>
           <t>Use Relevant Metrics</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D228" t="inlineStr">
         <is>
           <t>Use metrics appropriate to the problem type and business goal. Ensures the model is evaluated in a way that reflects real-world impact.
 This should change to be more specific. Define Thresholds. Test Thresholds, recommend based on X.</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
         <is>
           <t>Model Evaluation</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
+      <c r="C229" t="inlineStr">
         <is>
           <t>Keep Hold Out</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>Evaluate performance on a hold-out test set. Provides an unbiased estimate of generalization performance.</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
         <is>
           <t>Model Evaluation</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="C230" t="inlineStr">
         <is>
           <t>Review Overfitting</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D230" t="inlineStr">
         <is>
           <t>Check for overfitting by comparing training and test results. Identifies models that may not perform well in production.</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="D231" t="inlineStr">
         <is>
           <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
         <is>
           <t>Model Interpretability</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D232" t="inlineStr">
         <is>
           <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
         <is>
           <t>Model Interpretability</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
+      <c r="C233" t="inlineStr">
         <is>
           <t>Explain Selected Features using Words</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="D233" t="inlineStr">
         <is>
           <t>Utilize feature importance metrics to visualize and explain.</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
         <is>
           <t>Model Interpretability</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
+      <c r="C234" t="inlineStr">
         <is>
           <t>Results/Outcome should not be shocking</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="D234" t="inlineStr">
         <is>
           <t xml:space="preserve">This should be a formal step as engagement along the way is predicated on this as a core tenet and principle. If people seem shocked, embed stronger components earlier in process. </t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
         <is>
           <t>Model Interpretability</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
+      <c r="C235" t="inlineStr">
         <is>
           <t>Document Beyond Communciation</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>Document model behavior and major drivers. Supports stakeholder understanding and auditability.</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
+      <c r="D236" t="inlineStr">
         <is>
           <t>Deployment is the process of integrating the trained model into a production environment where it can generate real-world predictions. This may involve APIs, batch pipelines, streaming systems, or embedded applications. Considerations include scalability, latency, reliability, and versioning. Deployment turns a model from an experiment into a usable product. The goal is to make the model usable and operational in real-world settings.</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
+      <c r="C237" t="inlineStr">
         <is>
           <t>Package Model for Deployment with everything necessary</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D237" t="inlineStr">
         <is>
           <t>Package the model with all required preprocessing steps. Ensures predictions in production match training conditions.</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
+      <c r="C238" t="inlineStr">
         <is>
           <t>Test in different environments</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="D238" t="inlineStr">
         <is>
           <t>Test the model in a staging or test environment. Utilize Dedicated Environment. Reduces risk of failures in production.</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
         <is>
           <t>Deployment</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
+      <c r="C239" t="inlineStr">
         <is>
           <t>Version Control</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="D239" t="inlineStr">
         <is>
           <t>Create a versioned and reproducible deployment artifact. Supports rollback, auditing, and maintenance.</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
         <is>
           <t>Monitoring</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="D240" t="inlineStr">
         <is>
           <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
         <is>
           <t>Monitoring</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="C241" t="inlineStr">
         <is>
           <t>Overtime Perforamnce Monitoring</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D241" t="inlineStr">
         <is>
           <t>Track model performance metrics over time. Detects degradation or drift after deployment.</t>
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
         <is>
           <t>Monitoring</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
+      <c r="C242" t="inlineStr">
         <is>
           <t>Monitor Input Drift</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="D242" t="inlineStr">
         <is>
           <t>Monitor input data distributions for drift. Identifies changes in data that could affect predictions.</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
         <is>
           <t>Monitoring</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
+      <c r="C243" t="inlineStr">
         <is>
           <t>Clearly define production context windows</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="D243" t="inlineStr">
         <is>
           <t>Define triggers for retraining or model review. Ensures timely corrective action when performance declines.</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
         <is>
           <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="D244" t="inlineStr">
         <is>
           <t>This step examines whether the model produces systematically unfair or harmful outcomes across different groups. It includes analyzing data representation, outcome disparities, and unintended correlations. Ethical considerations may involve transparency, consent, explainability, and regulatory compliance. Addressing bias and fairness is essential for responsible, trustworthy, and legally compliant ML systems.</t>
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
         <is>
           <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
+      <c r="C245" t="inlineStr">
         <is>
           <t>Review Demographics</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="D245" t="inlineStr">
         <is>
           <t>Evaluate model performance across key demographic or operational groups. Identifies potential unfair or unequal outcomes.</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
         <is>
           <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
+      <c r="C246" t="inlineStr">
         <is>
           <t>Test unitended discrimination</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="D246" t="inlineStr">
         <is>
           <t>Review sensitive features and proxy variables. Prevents unintended discrimination.</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Machine Learning Lifecycle</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Machine Learning Lifecycle</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
         <is>
           <t>Bias, Fairness, and Ethics</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
+      <c r="C247" t="inlineStr">
         <is>
           <t>Document Fairness Checks</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D247" t="inlineStr">
         <is>
           <t>Document fairness checks and mitigation steps. Supports transparency, accountability, and compliance.</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
+    <row r="248">
+      <c r="A248" t="inlineStr">
         <is>
           <t>Measuing Effectiveness</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="B248" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
+      <c r="C248" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D248" t="inlineStr">
         <is>
           <t>How can one measure how effective/ineffective a particular communication was?</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
+    <row r="249">
+      <c r="A249" t="inlineStr">
         <is>
           <t>Message Spareness</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B249" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
+      <c r="C249" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D249" t="inlineStr">
         <is>
           <t>Utilize a less is more approach, whether that is Slides, Words, Pages, Etc. Less is more.</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
+    <row r="250">
+      <c r="A250" t="inlineStr">
         <is>
           <t>Model Evaluation</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B250" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
+      <c r="C250" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D250" t="inlineStr">
         <is>
           <t>Process of measuring how well a trained model performs using appropriate metrics and test data. This step assesses predictive accuracy, generalization, and robustness. Different metrics are used depending on the problem type, such as accuracy, F1 score, RMSE, or AUC. Evaluation ensures the model meets performance expectations before deployment, and results often determine whether a model is production-ready.</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
+    <row r="251">
+      <c r="A251" t="inlineStr">
         <is>
           <t>Model Evaluation</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
         <is>
           <t>Test Relative to Baseline</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
+      <c r="D251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
         <is>
           <t>Model Evaluation</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
         <is>
           <t>Use Relevant Metrics</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D252" t="inlineStr">
         <is>
           <t>Use metrics appropriate to the problem type and business goal. Ensures the model is evaluated in a way that reflects real-world impact.
 This should change to be more specific. Define Thresholds. Test Thresholds, recommend based on X.</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
+    <row r="253">
+      <c r="A253" t="inlineStr">
         <is>
           <t>Model Evaluation</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
         <is>
           <t>Keep Hold Out</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D253" t="inlineStr">
         <is>
           <t>Evaluate performance on a hold-out test set. Provides an unbiased estimate of generalization performance.</t>
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
+    <row r="254">
+      <c r="A254" t="inlineStr">
         <is>
           <t>Model Evaluation</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
         <is>
           <t>Review Overfitting</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="D254" t="inlineStr">
         <is>
           <t>Check for overfitting by comparing training and test results. Identifies models that may not perform well in production.</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
+    <row r="255">
+      <c r="A255" t="inlineStr">
         <is>
           <t>Model Interpretability</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B255" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C255" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D255" t="inlineStr">
         <is>
           <t>Process of explaining how a model makes predictions and which features influence its decisions. This may involve feature importance, partial dependence plots, SHAP values, or simpler surrogate models. Interpretability helps stakeholders understand, trust, and validate the model’s behavior. It is especially important in regulated or high-impact decision environments.</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
+    <row r="256">
+      <c r="A256" t="inlineStr">
         <is>
           <t>Model Interpretability</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
         <is>
           <t>Explain Selected Features using Words</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D256" t="inlineStr">
         <is>
           <t>Utilize feature importance metrics to visualize and explain.</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
+    <row r="257">
+      <c r="A257" t="inlineStr">
         <is>
           <t>Model Interpretability</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
         <is>
           <t>Results/Outcome should not be shocking</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D257" t="inlineStr">
         <is>
           <t xml:space="preserve">This should be a formal step as engagement along the way is predicated on this as a core tenet and principle. If people seem shocked, embed stronger components earlier in process. </t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
+    <row r="258">
+      <c r="A258" t="inlineStr">
         <is>
           <t>Model Interpretability</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
         <is>
           <t>Document Beyond Communciation</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="D258" t="inlineStr">
         <is>
           <t>Document model behavior and major drivers. Supports stakeholder understanding and auditability.</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
+    <row r="259">
+      <c r="A259" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
+      <c r="C259" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="D259" t="inlineStr">
         <is>
           <t>The process of choosing the most appropriate algorithm or model type for a given problem and dataset. This decision is based on factors such as data size, feature structure, interpretability needs, computational constraints, and performance requirements. Multiple candidate models are often tested and compared using consistent evaluation methods. The objective is to identify the model that provides the best balance between accuracy, stability, and practical usability.
 Similar to the process of engagement and audit followed in Feature Selection, it is critically important that actions are documented, defensible and clearly and consistently articulated to stakeholders in a meaningful manner.</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
+    <row r="260">
+      <c r="A260" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
         <is>
           <t>Define Baseline</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
+      <c r="D260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
         <is>
           <t>Document Results and Choice</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="D261" t="inlineStr">
         <is>
           <t>Ensure that final selection is documented and agreed by appropriate stakeholders, who have been part of entire development journey, understand and are aware.</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
+    <row r="262">
+      <c r="A262" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
         <is>
           <t>Define Validation Approach in Advance</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
+      <c r="D262" t="inlineStr">
         <is>
           <t>Use cross-validation or a structured validation approach. Provides a more reliable estimate of model performance.</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
+    <row r="263">
+      <c r="A263" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
         <is>
           <t>Validate no Leakage</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="D263" t="inlineStr">
         <is>
           <t>Ensure no data leakage between training and validation sets. Prevents overly optimistic performance estimates.</t>
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
+    <row r="264">
+      <c r="A264" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
         <is>
           <t>Validate consistency over time</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="D264" t="inlineStr">
         <is>
           <t>Confirm performance stability across folds or time splits. Indicates the model is robust and generalizable.</t>
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
+    <row r="265">
+      <c r="A265" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
         <is>
           <t>How will Model Learn?</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D265" t="inlineStr">
         <is>
           <t>Must select an appropriate learning method. Supervised, Unsupervised, Semi-Supervised, Reinforcement</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
+    <row r="266">
+      <c r="A266" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
         <is>
           <t>What Problem is the Model Solving?</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D266" t="inlineStr">
         <is>
           <t>Must select an appropriate method. Classification, Regression, Clustering, Dimensionality Reduction, etc.</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
+    <row r="267">
+      <c r="A267" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
         <is>
           <t>What Model/Algo is being used to solve the problem</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D267" t="inlineStr">
         <is>
           <t>Document founational assessment at the outset, can revisit during Model Selection.</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
+    <row r="268">
+      <c r="A268" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
         <is>
           <t>Select Model(s) based on Objective</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D268" t="inlineStr">
         <is>
           <t xml:space="preserve">Define what the objective of the model work is, state what is being measured and why. 
 Document all models which will be considered, including why they are appropriate and where models are excluded, insure rationale available. Compare multiple model types using the same validation approach. Ensures a fair comparison and better-informed model choice.
@@ -5262,844 +6210,1560 @@
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
+    <row r="269">
+      <c r="A269" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
         <is>
           <t>Create and Understand Baseline</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D269" t="inlineStr">
         <is>
           <t>Create Simplified Baseline Model, use this are reference. Ensure that this is communicated to Stakeholders, so they understand both the benchmark and expectation, to determine relevance. Should align with Goals.</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
+    <row r="270">
+      <c r="A270" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
         <is>
           <t>Performance vs Cost vs Practicality</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="D270" t="inlineStr">
         <is>
           <t>Consider interpretability, performance, and computational cost. Balances practical constraints with predictive accuracy.</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
+    <row r="271">
+      <c r="A271" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
         <is>
           <t>How Many Examples are Needed?</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D271" t="inlineStr">
         <is>
           <t>Distinct for every type of Method or approach. Need to be comfortable that the dataset has enough examples and that they represent a population to which you believe is representive.</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
+    <row r="272">
+      <c r="A272" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B272" t="inlineStr">
         <is>
           <t>Consideration</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
+      <c r="C272" t="inlineStr">
         <is>
           <t>Understand what your model is actually solving and how.</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="D272" t="inlineStr">
         <is>
           <t>Models will cheat and can solve problems which appear to be optimal, but they might not be solving what you expect or require, they might be finding patterns in the data which you do not see. An Example of this would a classification model with Wolves and Dogs,  many wolf photos happened to be taken in snowy environments, while dog photos were often taken indoors or on grass. The model learned to detect snow, not animals.</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
+    <row r="273">
+      <c r="A273" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B273" t="inlineStr">
         <is>
           <t>Consideration</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="C273" t="inlineStr">
         <is>
           <t>Speed vs Accuracy</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D273" t="inlineStr">
         <is>
           <t>The most accurate model is not always the most valuable. Delivering a good solution quickly often creates more business value than spending significant time chasing small improvements in performance.</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
+    <row r="274">
+      <c r="A274" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B274" t="inlineStr">
         <is>
           <t>Consideration</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
+      <c r="C274" t="inlineStr">
         <is>
           <t>Accuracy vs Repeatability</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D274" t="inlineStr">
         <is>
           <t>A highly accurate result has limited value if it cannot be reproduced consistently. Prioritize workflows, data pipelines, and model training processes that generate reliable and repeatable outcomes over one-time exceptional results.</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
+    <row r="275">
+      <c r="A275" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B275" t="inlineStr">
         <is>
           <t>Consideration</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
+      <c r="C275" t="inlineStr">
         <is>
           <t>Correlation vs Causation</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="D275" t="inlineStr">
         <is>
           <t>Machine learning identifies relationships in data but does not prove why those relationships exist. Treat model outputs as evidence of association and rely on experimentation or domain expertise to establish causal conclusions.</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
+    <row r="276">
+      <c r="A276" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B276" t="inlineStr">
         <is>
           <t>Consideration</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
+      <c r="C276" t="inlineStr">
         <is>
           <t>Stability over Uniqueness</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
+      <c r="D276" t="inlineStr">
         <is>
           <t>Prefer models that perform consistently across different datasets and over time rather than those that achieve exceptional results only under specific conditions. Reliable, generalizable models are more valuable than highly specialized ones that are difficult to maintain.</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
+    <row r="277">
+      <c r="A277" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B277" t="inlineStr">
         <is>
           <t>Consideration</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
+      <c r="C277" t="inlineStr">
         <is>
           <t>Interpretability over Novelty</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
+      <c r="D277" t="inlineStr">
         <is>
           <t>A simple model that stakeholders understand and trust is often more useful than a complex state-of-the-art model with marginal performance gains. Choose complexity only when it delivers meaningful improvements that justify reduced transparency.</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
+    <row r="278">
+      <c r="A278" t="inlineStr">
         <is>
           <t>Model Selection</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B278" t="inlineStr">
         <is>
           <t>Consideration</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
+      <c r="C278" t="inlineStr">
         <is>
           <t>Repeatability over Perfection</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="D278" t="inlineStr">
         <is>
           <t>Machine learning is an iterative process, not a search for a flawless model. Build solutions that others can rerun, validate, and improve, knowing that incremental refinement typically delivers more long-term value than pursuing perfection from the outset.</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
+    <row r="279">
+      <c r="A279" t="inlineStr">
         <is>
           <t>Monitoring</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B279" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
+      <c r="C279" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
+      <c r="D279" t="inlineStr">
         <is>
           <t>Ongoing process of tracking model performance and data quality after deployment. It helps detect issues such as data drift, concept drift, performance degradation, or system failures. Monitoring ensures the model continues to perform as expected over time. When problems are detected, retraining or model updates may be required.</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
+    <row r="280">
+      <c r="A280" t="inlineStr">
         <is>
           <t>Monitoring</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B280" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
+      <c r="C280" t="inlineStr">
         <is>
           <t>Overtime Perforamnce Monitoring</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
+      <c r="D280" t="inlineStr">
         <is>
           <t>Track model performance metrics over time. Detects degradation or drift after deployment.</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
+    <row r="281">
+      <c r="A281" t="inlineStr">
         <is>
           <t>Monitoring</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B281" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
+      <c r="C281" t="inlineStr">
         <is>
           <t>Monitor Input Drift</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="D281" t="inlineStr">
         <is>
           <t>Monitor input data distributions for drift. Identifies changes in data that could affect predictions.</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
+    <row r="282">
+      <c r="A282" t="inlineStr">
         <is>
           <t>Monitoring</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B282" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
+      <c r="C282" t="inlineStr">
         <is>
           <t>Clearly define production context windows</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D282" t="inlineStr">
         <is>
           <t>Define triggers for retraining or model review. Ensures timely corrective action when performance declines.</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
+    <row r="283">
+      <c r="A283" t="inlineStr">
         <is>
           <t>Organization - Definition</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B283" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
+      <c r="C283" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
+      <c r="D283" t="inlineStr">
         <is>
           <t>List used to manage the default order of items as stored in the Notes Sheet. Specifically, there is a heirarchical order created and expected to prioritize how items are stored and filter, this list maintains that order and can be used as guidance to understand.</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Persuasion</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Persuasion</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Reciprocity</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>People say yes to those who said yes to them. Invest in those you want to invest in you. Be the first to give, and do it personalized and unexpected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Persuasion</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Scarcity</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>People want what is in short supply. Tell them what they gain, what is unique and what they stand to lose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Persuasion</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Authority</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Make sure people know your expertise. Don't be arrogant. Specifically if they don't know you, get a third party to introduce you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Persuasion</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Consistency</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>People like to be consistent when they take a public opinion. Get them to take a small step first, then they will be willing to take a big step in the future.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Persuasion</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Liking</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>People want to be liked and work with people who like them. We like people who are similar to us, compliment us, cooperate with us</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Persuasion</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Consensus</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>People follow the leads of others.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B291" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
+      <c r="C291" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D291" t="inlineStr">
         <is>
           <t>A Clear, Concise and explicit definition of the problem at hand, or a "Problem Statement". A problem statement should be simple, straight forward and easy to understand. SMART is a specific methodlogy which is popular.  Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk the likelihood of change to project purpose, scope or priority likely.</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
+    <row r="292">
+      <c r="A292" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
         <is>
           <t>Desired State Metrics</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="D292" t="inlineStr">
         <is>
           <t>Describe the target outcomes or performance levels that define success. They show what improvement looks like in measurable terms and help guide priorities and actions. This is important because clear targets create alignment, focus efforts, and allow teams to track progress toward meaningful results.</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
+    <row r="293">
+      <c r="A293" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
         <is>
           <t>Current State Analysis</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="D293" t="inlineStr">
         <is>
           <t>Describes how the process, system, or situation is functioning today. It provides a factual, objective picture of what is happening, without assumptions or solutions. This is important because it ensures everyone has a shared understanding of reality before trying to fix the problem.</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
+    <row r="294">
+      <c r="A294" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
         <is>
           <t>Root Cause Assessment</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
+      <c r="D294" t="inlineStr">
         <is>
           <t>Identifies the underlying reasons why the problem exists. Rather than focusing on symptoms, it explores the fundamental drivers using methods such as the “5 Whys” or cause-and-effect analysis. This is important because addressing root causes leads to sustainable improvements, while only treating symptoms often results in recurring issues.</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
+    <row r="295">
+      <c r="A295" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
         <is>
           <t>Historical Overview</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="D295" t="inlineStr">
         <is>
           <t>Summarizes what actions, initiatives, or attempts have already been made to address the problem. It explains what was tried, what worked, and what did not. This is important because it prevents repeating past mistakes and helps build on lessons learned.</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
+    <row r="296">
+      <c r="A296" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
         <is>
           <t>Baseline Metrics (Current State)</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
+      <c r="D296" t="inlineStr">
         <is>
           <t>Quantify the current state of the problem using measurable data such as performance indicators, volumes, timelines, or quality measures. These metrics provide an objective reference point for understanding the scope and impact of the issue. This is important because improvement cannot be measured without a clear starting baseline.</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
+    <row r="297">
+      <c r="A297" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B297" t="inlineStr">
         <is>
           <t>Guidance</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
+      <c r="C297" t="inlineStr">
         <is>
           <t>Understand KPIs which are meaningful.</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
+      <c r="D297" t="inlineStr">
         <is>
           <t>Attempt to explicitly define outcomes and relevant KPIs for those outcomes. Where that can not happen, it is important to understand why that can not happen. What is happening if we don't have and follow metrics. IE. The Account Opening Process is not efficient and needs to improve, The Internet Banking Experience is poor, and does not attract customers. How do you monitor this, how can you define this, how can you prove this,  how do you expect this to change and measure that change.
 How will the project and efforts be measured where success can not be objectively measured? How will resources be allocated when it remains unclear what benefit or risk exists.</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
+    <row r="298">
+      <c r="A298" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B298" t="inlineStr">
         <is>
           <t>Guidance</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
+      <c r="C298" t="inlineStr">
         <is>
           <t>What Lens is Problem Defined?</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="D298" t="inlineStr">
         <is>
           <t>Must be careful at how problem is defined. Is it defined in the context of the already identified solution, has it been validated and is the problem distinct from the analysis and potential solution, or have we leaked into the process.</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
+    <row r="299">
+      <c r="A299" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
+      <c r="B299" t="inlineStr">
         <is>
           <t>Guidance</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
+      <c r="C299" t="inlineStr">
         <is>
           <t>Stakeholder Investment?</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
+      <c r="D299" t="inlineStr">
         <is>
           <t>How Invested are stakeholders in defining the problem? What is their view of the process/ project, how invested, interested and engaged are they. What are their personal goals and motivation, speed, accuracy, validation of ideology?</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
+    <row r="300">
+      <c r="A300" t="inlineStr">
         <is>
           <t>Problem Definition</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="B300" t="inlineStr">
         <is>
           <t>Guidance</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
+      <c r="C300" t="inlineStr">
         <is>
           <t>Really Understand Problem Statement</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
+      <c r="D300" t="inlineStr">
         <is>
           <t>Proceed with extreme caution where the problem statement is incomplete, or ill-stated, as this is likely indicative that the problem is not truly understood or at a minimum defined. Where this is the case, the project will be at extreme risk and the likelihood of not meeting expectations, frustration, or material change to purpose, scope or priority is inevitable.</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
+    <row r="301">
+      <c r="A301" t="inlineStr">
         <is>
           <t>Re-enforce the Message</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
+      <c r="B301" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
+      <c r="C301" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
+      <c r="D301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
         <is>
           <t>Regularization</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="B302" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
+      <c r="C302" t="inlineStr">
         <is>
           <t>ElasticNet</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
+      <c r="D302" t="inlineStr">
         <is>
           <t>Approach which combines L1 and L2 Regularization.</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
+    <row r="303">
+      <c r="A303" t="inlineStr">
         <is>
           <t>Regularization</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="B303" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
+      <c r="C303" t="inlineStr">
         <is>
           <t>Lasso</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
+      <c r="D303" t="inlineStr">
         <is>
           <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the absolute values of the coefficients as a penalty term. This leads to sparse models, as some coefficients become exactly zero</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
+    <row r="304">
+      <c r="A304" t="inlineStr">
         <is>
           <t>Regularization</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B304" t="inlineStr">
         <is>
           <t>Data Preparation</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
+      <c r="C304" t="inlineStr">
         <is>
           <t>Ridge</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
+      <c r="D304" t="inlineStr">
         <is>
           <t>Technique used to prevent overfitting by adding penalty term to loss function. Adds the squared values of the coefficients as a penalty term. This increases the cost of larger parameters, encouraging the model to distribute parameters waiting This shrinks the coefficients but does not eliminate them.</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Technology Adoption</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Notes from Books</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Technology Trap</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Industrial Revolution Changed the World. Displaced the current order, changed distribution of income from Workers to Owners.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Technology Adoption</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Notes from Books</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Technology Trap</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Differences in global income distribution have been attributed to adoption of technology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Technology Adoption</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Notes from Books</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Technology Trap</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Lamplighters, out of Business due to electricity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Technology Adoption</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Notes from Books</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Technology Trap</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Over 1 Million truck drivers - High School Educated, Middle Aged, Male. What do they do when self driving cars put them out of work?</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Technology Adoption</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Notes from Books</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Technology Trap</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Enabling vs Replacing Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B310" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
+      <c r="C310" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="D310" t="inlineStr">
         <is>
           <t>Process of fitting a machine learning model to data so it can learn the relationships between input features and the target variable. During training, the model adjusts its internal parameters to minimize a loss function. This step typically occurs on a designated training dataset. The quality of training directly affects the model’s ability to generalize to new, unseen data.</t>
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
+    <row r="311">
+      <c r="A311" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
         <is>
           <t>Train, Test, Validation Split</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="D311" t="inlineStr">
         <is>
           <t>Is split between Training, Testing and Validation appropriate, fair and responsible. Validate and document.</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
+    <row r="312">
+      <c r="A312" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
         <is>
           <t>Convergence Achieved?</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="D312" t="inlineStr">
         <is>
           <t>Verify model converges and loss decreases during training. Confirms the model is learning meaningful patterns.</t>
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
+    <row r="313">
+      <c r="A313" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Process Step</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
         <is>
           <t>Logging of Parameters</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
+      <c r="D313" t="inlineStr">
         <is>
           <t>Log model parameters, features, training configuration and results. Supports reproducibility and troubleshooting.</t>
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
+    <row r="314">
+      <c r="A314" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Activation Function</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Select a Activation Function based on Learning Paradigm and Method, potentially trying multiple variants across grid search.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
         <is>
           <t>Warning</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
+      <c r="C315" t="inlineStr">
         <is>
           <t>Any dataset can be optimized</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
+      <c r="D315" t="inlineStr">
         <is>
           <t>Any data set can be optimized, even when there is NO relation it will generalize. Remember the goal, ability to generalize, not simply predict training.</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Activation Function</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Leaky Relu</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Activation Function</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Relu</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Activation Function</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Sigmoid</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Activation Function</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Softmax</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Activation Function</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Tanh</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
         <is>
           <t>Understand Your Audience</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B321" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
+      <c r="C321" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
+      <c r="D321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Understand Your Audience</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Who is it?</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>It might be extremely broad, it might change for a similiar piece of work, or the work might be done with a single person in mind, and little focus or regard is paid to others, regardless of the level of interaction to which they will have.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Understand Your Audience</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>What do they want?</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The more we know about the motivations and incentives of decision makers, the more we can control the communication. </t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Understand Your Audience</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Are they likely to Care?</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Understand Your Audience</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Getting CEO to Pick</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>How to get a CEO to remove a soft drink from Japan without telling them to remove a soft drink from Japan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Understand Your Audience</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Consideration</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Stress Induced U Curve</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>High Pressure Decision Making: The inverted U shape Curve, Stress vs Performance. No one knows exactly where it is for each individual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Understand Your Audience</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Cuban Missile Crisis</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Asymmetric Information, Deception, Misreading Adversarial Strength, Attempting to disrupt competitor. Fear is the reigning notion. People don't read the data well when fear is involved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
         <is>
           <t>Understand Your Message</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B328" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
+      <c r="C328" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
+      <c r="D328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Do not Assume it is Dull.</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Even if it might be less than impressive, or revolutionary for you, do not convey this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Do you actually understand it?</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>You must understand it, backforward and center. Message, Purpose. Reason. All can be different, might have different motivations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Clarity for all.</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Is the message clear to you, will it be clear to them?</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>BLUF</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Bottom Line Up Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Tell the Story, Do not Show it.</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Storytelling beats data 100% of the time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Understand Your Message</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Where are you truly at?</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Is the glass half full, half empty. If it's half full, do you have what you really want in the glass?</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
         <is>
           <t>Understand Your Strategy</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B335" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
+      <c r="C335" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
+      <c r="D335" t="inlineStr">
         <is>
           <t>Beyond understanding Your Message, you need to think about how you are going to articulate your story, your goals, motivation, priority. Reconizing differences between things that have great personal meaning, business relevance, or simply mandated work.</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
+    <row r="336">
+      <c r="A336" t="inlineStr">
         <is>
           <t>Understand Your Visuals</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B336" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
+      <c r="C336" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
+      <c r="D336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Understand Your Visuals</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Interesting and Engaging Visuals, Minimal Words.</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>80% Salient might be better than 100% accurate</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Understand Your Visuals</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Process Step</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Simplicity over Complexity</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Are they Simple and Clear?</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Understand Your Visuals</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Will they understand?</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>People are easily distractible, so they might not recognize stuff that is immediately in front of them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Understand Your Visuals</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Eyes Not Minds</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B341" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
+      <c r="C341" t="inlineStr">
         <is>
           <t>Definition</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
+      <c r="D341" t="inlineStr">
         <is>
           <t>Validation is the process of assessing model performance on data that was not used during training. It is used to tune hyperparameters, compare models, and detect overfitting. Common approaches include hold-out validation and cross-validation techniques. The purpose is to estimate how well the model will perform on unseen data.</t>
         </is>
